--- a/research/traditional_assets/database/data/luxembourg/luxembourg_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_retail_distributors.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07085377930559372</v>
+        <v>0.07071084698000557</v>
       </c>
       <c r="C2">
-        <v>725.1990386554338</v>
+        <v>719.1082284158318</v>
       </c>
       <c r="D2">
-        <v>691.8990386554339</v>
+        <v>694.1292284158319</v>
       </c>
       <c r="E2">
-        <v>-470</v>
+        <v>-461.679</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.321</v>
       </c>
       <c r="G2">
         <v>33.3</v>
@@ -1451,28 +1451,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4185463</v>
       </c>
       <c r="N2">
-        <v>92.22499999999999</v>
+        <v>91.80645369999999</v>
       </c>
       <c r="O2">
-        <v>23.000915</v>
+        <v>22.89652955278</v>
       </c>
       <c r="P2">
-        <v>69.224085</v>
+        <v>68.90992414722</v>
       </c>
       <c r="Q2">
-        <v>109.124085</v>
+        <v>108.80992414722</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07085377930559372</v>
+        <v>0.07104373250505613</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381922</v>
+        <v>0.5829961317564927</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>220.3459927850276</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07071084698000557</v>
+        <v>0.07056791465441742</v>
       </c>
       <c r="C3">
-        <v>719.1082284158318</v>
+        <v>713.0318417546629</v>
       </c>
       <c r="D3">
-        <v>694.1292284158319</v>
+        <v>696.373841754663</v>
       </c>
       <c r="E3">
-        <v>-461.679</v>
+        <v>-453.358</v>
       </c>
       <c r="F3">
-        <v>8.321</v>
+        <v>16.642</v>
       </c>
       <c r="G3">
         <v>33.3</v>
@@ -1533,28 +1533,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M3">
-        <v>0.4185463</v>
+        <v>0.8370926</v>
       </c>
       <c r="N3">
-        <v>91.80645369999999</v>
+        <v>91.38790739999999</v>
       </c>
       <c r="O3">
-        <v>22.89652955278</v>
+        <v>22.79214410556</v>
       </c>
       <c r="P3">
-        <v>68.90992414722</v>
+        <v>68.59576329443999</v>
       </c>
       <c r="Q3">
-        <v>108.80992414722</v>
+        <v>108.49576329444</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07104373250505613</v>
+        <v>0.07123756230042594</v>
       </c>
       <c r="T3">
-        <v>0.5829961317564927</v>
+        <v>0.587472570448636</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>220.3459927850276</v>
+        <v>110.1729963925138</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07056791465441742</v>
+        <v>0.07042498232882927</v>
       </c>
       <c r="C4">
-        <v>713.0318417546629</v>
+        <v>706.9700190509257</v>
       </c>
       <c r="D4">
-        <v>696.373841754663</v>
+        <v>698.6330190509257</v>
       </c>
       <c r="E4">
-        <v>-453.358</v>
+        <v>-445.037</v>
       </c>
       <c r="F4">
-        <v>16.642</v>
+        <v>24.963</v>
       </c>
       <c r="G4">
         <v>33.3</v>
@@ -1615,28 +1615,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M4">
-        <v>0.8370926</v>
+        <v>1.2556389</v>
       </c>
       <c r="N4">
-        <v>91.38790739999999</v>
+        <v>90.9693611</v>
       </c>
       <c r="O4">
-        <v>22.79214410556</v>
+        <v>22.68775865834</v>
       </c>
       <c r="P4">
-        <v>68.59576329443999</v>
+        <v>68.28160244166</v>
       </c>
       <c r="Q4">
-        <v>108.49576329444</v>
+        <v>108.18160244166</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07123756230042594</v>
+        <v>0.07143538858642193</v>
       </c>
       <c r="T4">
-        <v>0.587472570448636</v>
+        <v>0.5920413068457719</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>110.1729963925138</v>
+        <v>73.44866426167587</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07042498232882927</v>
+        <v>0.07028205000324113</v>
       </c>
       <c r="C5">
-        <v>706.9700190509257</v>
+        <v>700.9229025112193</v>
       </c>
       <c r="D5">
-        <v>698.6330190509257</v>
+        <v>700.9069025112193</v>
       </c>
       <c r="E5">
-        <v>-445.037</v>
+        <v>-436.716</v>
       </c>
       <c r="F5">
-        <v>24.963</v>
+        <v>33.284</v>
       </c>
       <c r="G5">
         <v>33.3</v>
@@ -1697,28 +1697,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M5">
-        <v>1.2556389</v>
+        <v>1.6741852</v>
       </c>
       <c r="N5">
-        <v>90.9693611</v>
+        <v>90.5508148</v>
       </c>
       <c r="O5">
-        <v>22.68775865834</v>
+        <v>22.58337321112</v>
       </c>
       <c r="P5">
-        <v>68.28160244166</v>
+        <v>67.96744158887999</v>
       </c>
       <c r="Q5">
-        <v>108.18160244166</v>
+        <v>107.86744158888</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07143538858642193</v>
+        <v>0.07163733625337618</v>
       </c>
       <c r="T5">
-        <v>0.5920413068457719</v>
+        <v>0.5967052252511816</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.44866426167587</v>
+        <v>55.0864981962569</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07028205000324113</v>
+        <v>0.07013911767765296</v>
       </c>
       <c r="C6">
-        <v>700.9229025112193</v>
+        <v>694.8906361995831</v>
       </c>
       <c r="D6">
-        <v>700.9069025112193</v>
+        <v>703.1956361995832</v>
       </c>
       <c r="E6">
-        <v>-436.716</v>
+        <v>-428.395</v>
       </c>
       <c r="F6">
-        <v>33.284</v>
+        <v>41.605</v>
       </c>
       <c r="G6">
         <v>33.3</v>
@@ -1779,28 +1779,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M6">
-        <v>1.6741852</v>
+        <v>2.0927315</v>
       </c>
       <c r="N6">
-        <v>90.5508148</v>
+        <v>90.1322685</v>
       </c>
       <c r="O6">
-        <v>22.58337321112</v>
+        <v>22.4789877639</v>
       </c>
       <c r="P6">
-        <v>67.96744158887999</v>
+        <v>67.65328073609999</v>
       </c>
       <c r="Q6">
-        <v>107.86744158888</v>
+        <v>107.5532807361</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07163733625337618</v>
+        <v>0.07184353545016102</v>
       </c>
       <c r="T6">
-        <v>0.5967052252511816</v>
+        <v>0.6014673314124946</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.0864981962569</v>
+        <v>44.06919855700551</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07013911767765296</v>
+        <v>0.06999618535206482</v>
       </c>
       <c r="C7">
-        <v>694.8906361995831</v>
+        <v>688.8733660679201</v>
       </c>
       <c r="D7">
-        <v>703.1956361995832</v>
+        <v>705.4993660679202</v>
       </c>
       <c r="E7">
-        <v>-428.395</v>
+        <v>-420.074</v>
       </c>
       <c r="F7">
-        <v>41.605</v>
+        <v>49.926</v>
       </c>
       <c r="G7">
         <v>33.3</v>
@@ -1861,28 +1861,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M7">
-        <v>2.0927315</v>
+        <v>2.5112778</v>
       </c>
       <c r="N7">
-        <v>90.1322685</v>
+        <v>89.71372219999999</v>
       </c>
       <c r="O7">
-        <v>22.4789877639</v>
+        <v>22.37460231668</v>
       </c>
       <c r="P7">
-        <v>67.65328073609999</v>
+        <v>67.33911988332</v>
       </c>
       <c r="Q7">
-        <v>107.5532807361</v>
+        <v>107.23911988332</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07184353545016102</v>
+        <v>0.07205412186389874</v>
       </c>
       <c r="T7">
-        <v>0.6014673314124946</v>
+        <v>0.6063307589814951</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.06919855700551</v>
+        <v>36.72433213083794</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06999618535206482</v>
+        <v>0.06985325302647667</v>
       </c>
       <c r="C8">
-        <v>688.8733660679201</v>
+        <v>682.8712399870257</v>
       </c>
       <c r="D8">
-        <v>705.4993660679202</v>
+        <v>707.8182399870257</v>
       </c>
       <c r="E8">
-        <v>-420.074</v>
+        <v>-411.753</v>
       </c>
       <c r="F8">
-        <v>49.926</v>
+        <v>58.24699999999999</v>
       </c>
       <c r="G8">
         <v>33.3</v>
@@ -1943,28 +1943,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M8">
-        <v>2.5112778</v>
+        <v>2.929824099999999</v>
       </c>
       <c r="N8">
-        <v>89.71372219999999</v>
+        <v>89.29517589999999</v>
       </c>
       <c r="O8">
-        <v>22.37460231668</v>
+        <v>22.27021686946</v>
       </c>
       <c r="P8">
-        <v>67.33911988332</v>
+        <v>67.02495903053999</v>
       </c>
       <c r="Q8">
-        <v>107.23911988332</v>
+        <v>106.92495903054</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07205412186389874</v>
+        <v>0.07226923701771684</v>
       </c>
       <c r="T8">
-        <v>0.6063307589814951</v>
+        <v>0.6112987763906893</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.72433213083794</v>
+        <v>31.47799896928966</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06985325302647666</v>
+        <v>0.06971032070088853</v>
       </c>
       <c r="C9">
-        <v>682.8712399870259</v>
+        <v>676.8844077782243</v>
       </c>
       <c r="D9">
-        <v>707.8182399870259</v>
+        <v>710.1524077782243</v>
       </c>
       <c r="E9">
-        <v>-411.753</v>
+        <v>-403.432</v>
       </c>
       <c r="F9">
-        <v>58.24700000000001</v>
+        <v>66.568</v>
       </c>
       <c r="G9">
         <v>33.3</v>
@@ -2025,28 +2025,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M9">
-        <v>2.9298241</v>
+        <v>3.3483704</v>
       </c>
       <c r="N9">
-        <v>89.29517589999999</v>
+        <v>88.8766296</v>
       </c>
       <c r="O9">
-        <v>22.27021686946</v>
+        <v>22.16583142224</v>
       </c>
       <c r="P9">
-        <v>67.02495903053999</v>
+        <v>66.71079817776</v>
       </c>
       <c r="Q9">
-        <v>106.92495903054</v>
+        <v>106.61079817776</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07226923701771684</v>
+        <v>0.07248902858792231</v>
       </c>
       <c r="T9">
-        <v>0.6112987763906893</v>
+        <v>0.6163747941783442</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.47799896928965</v>
+        <v>27.54324909812845</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06971032070088853</v>
+        <v>0.06956738837530037</v>
       </c>
       <c r="C10">
-        <v>676.8844077782243</v>
+        <v>670.9130212456396</v>
       </c>
       <c r="D10">
-        <v>710.1524077782243</v>
+        <v>712.5020212456396</v>
       </c>
       <c r="E10">
-        <v>-403.432</v>
+        <v>-395.111</v>
       </c>
       <c r="F10">
-        <v>66.568</v>
+        <v>74.889</v>
       </c>
       <c r="G10">
         <v>33.3</v>
@@ -2107,28 +2107,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M10">
-        <v>3.3483704</v>
+        <v>3.766916699999999</v>
       </c>
       <c r="N10">
-        <v>88.8766296</v>
+        <v>88.4580833</v>
       </c>
       <c r="O10">
-        <v>22.16583142224</v>
+        <v>22.06144597502</v>
       </c>
       <c r="P10">
-        <v>66.71079817776</v>
+        <v>66.39663732497999</v>
       </c>
       <c r="Q10">
-        <v>106.61079817776</v>
+        <v>106.29663732498</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07248902858792231</v>
+        <v>0.07271365074208831</v>
       </c>
       <c r="T10">
-        <v>0.6163747941783442</v>
+        <v>0.6215623727964968</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.54324909812845</v>
+        <v>24.48288808722529</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06956738837530037</v>
+        <v>0.06942445604971223</v>
       </c>
       <c r="C11">
-        <v>670.9130212456396</v>
+        <v>664.9572342091024</v>
       </c>
       <c r="D11">
-        <v>712.5020212456396</v>
+        <v>714.8672342091024</v>
       </c>
       <c r="E11">
-        <v>-395.111</v>
+        <v>-386.79</v>
       </c>
       <c r="F11">
-        <v>74.889</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="G11">
         <v>33.3</v>
@@ -2189,28 +2189,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M11">
-        <v>3.766916699999999</v>
+        <v>4.185462999999999</v>
       </c>
       <c r="N11">
-        <v>88.4580833</v>
+        <v>88.039537</v>
       </c>
       <c r="O11">
-        <v>22.06144597502</v>
+        <v>21.9570605278</v>
       </c>
       <c r="P11">
-        <v>66.39663732497999</v>
+        <v>66.0824764722</v>
       </c>
       <c r="Q11">
-        <v>106.29663732498</v>
+        <v>105.9824764722</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07271365074208831</v>
+        <v>0.07294326449968025</v>
       </c>
       <c r="T11">
-        <v>0.6215623727964968</v>
+        <v>0.6268652309394974</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.48288808722529</v>
+        <v>22.03459927850276</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06942445604971223</v>
+        <v>0.06928152372412408</v>
       </c>
       <c r="C12">
-        <v>664.9572342091024</v>
+        <v>659.0172025377212</v>
       </c>
       <c r="D12">
-        <v>714.8672342091024</v>
+        <v>717.2482025377212</v>
       </c>
       <c r="E12">
-        <v>-386.79</v>
+        <v>-378.469</v>
       </c>
       <c r="F12">
-        <v>83.21000000000001</v>
+        <v>91.53100000000001</v>
       </c>
       <c r="G12">
         <v>33.3</v>
@@ -2271,28 +2271,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M12">
-        <v>4.185463</v>
+        <v>4.6040093</v>
       </c>
       <c r="N12">
-        <v>88.039537</v>
+        <v>87.62099069999999</v>
       </c>
       <c r="O12">
-        <v>21.9570605278</v>
+        <v>21.85267508058</v>
       </c>
       <c r="P12">
-        <v>66.0824764722</v>
+        <v>65.76831561941999</v>
       </c>
       <c r="Q12">
-        <v>105.9824764722</v>
+        <v>105.66831561942</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07294326449968025</v>
+        <v>0.07317803811699333</v>
       </c>
       <c r="T12">
-        <v>0.6268652309394974</v>
+        <v>0.6322872544340261</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.03459927850276</v>
+        <v>20.03145388954796</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06928152372412408</v>
+        <v>0.06913859139853591</v>
       </c>
       <c r="C13">
-        <v>659.0172025377212</v>
+        <v>653.0930841841216</v>
       </c>
       <c r="D13">
-        <v>717.2482025377212</v>
+        <v>719.6450841841216</v>
       </c>
       <c r="E13">
-        <v>-378.469</v>
+        <v>-370.148</v>
       </c>
       <c r="F13">
-        <v>91.53100000000001</v>
+        <v>99.852</v>
       </c>
       <c r="G13">
         <v>33.3</v>
@@ -2353,28 +2353,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M13">
-        <v>4.6040093</v>
+        <v>5.0225556</v>
       </c>
       <c r="N13">
-        <v>87.62099069999999</v>
+        <v>87.20244439999999</v>
       </c>
       <c r="O13">
-        <v>21.85267508058</v>
+        <v>21.74828963336</v>
       </c>
       <c r="P13">
-        <v>65.76831561941999</v>
+        <v>65.45415476663999</v>
       </c>
       <c r="Q13">
-        <v>105.66831561942</v>
+        <v>105.35415476664</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07317803811699333</v>
+        <v>0.07341814749833626</v>
       </c>
       <c r="T13">
-        <v>0.6322872544340261</v>
+        <v>0.6378325057352485</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.03145388954796</v>
+        <v>18.36216606541897</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06913859139853591</v>
+        <v>0.06899565907294775</v>
       </c>
       <c r="C14">
-        <v>653.0930841841216</v>
+        <v>647.1850392193762</v>
       </c>
       <c r="D14">
-        <v>719.6450841841216</v>
+        <v>722.0580392193763</v>
       </c>
       <c r="E14">
-        <v>-370.148</v>
+        <v>-361.827</v>
       </c>
       <c r="F14">
-        <v>99.852</v>
+        <v>108.173</v>
       </c>
       <c r="G14">
         <v>33.3</v>
@@ -2435,28 +2435,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M14">
-        <v>5.0225556</v>
+        <v>5.4411019</v>
       </c>
       <c r="N14">
-        <v>87.20244439999999</v>
+        <v>86.78389809999999</v>
       </c>
       <c r="O14">
-        <v>21.74828963336</v>
+        <v>21.64390418614</v>
       </c>
       <c r="P14">
-        <v>65.45415476663999</v>
+        <v>65.13999391386</v>
       </c>
       <c r="Q14">
-        <v>105.35415476664</v>
+        <v>105.03999391386</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07341814749833626</v>
+        <v>0.07366377663557214</v>
       </c>
       <c r="T14">
-        <v>0.6378325057352485</v>
+        <v>0.6435052340778785</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.36216606541897</v>
+        <v>16.94969175269443</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06899565907294775</v>
+        <v>0.06885272674735961</v>
       </c>
       <c r="C15">
-        <v>647.1850392193762</v>
+        <v>641.2932298686402</v>
       </c>
       <c r="D15">
-        <v>722.0580392193763</v>
+        <v>724.4872298686403</v>
       </c>
       <c r="E15">
-        <v>-361.827</v>
+        <v>-353.506</v>
       </c>
       <c r="F15">
-        <v>108.173</v>
+        <v>116.494</v>
       </c>
       <c r="G15">
         <v>33.3</v>
@@ -2517,28 +2517,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M15">
-        <v>5.4411019</v>
+        <v>5.859648200000001</v>
       </c>
       <c r="N15">
-        <v>86.78389809999999</v>
+        <v>86.3653518</v>
       </c>
       <c r="O15">
-        <v>21.64390418614</v>
+        <v>21.53951873892</v>
       </c>
       <c r="P15">
-        <v>65.13999391386</v>
+        <v>64.82583306108</v>
       </c>
       <c r="Q15">
-        <v>105.03999391386</v>
+        <v>104.72583306108</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07366377663557214</v>
+        <v>0.07391511807832514</v>
       </c>
       <c r="T15">
-        <v>0.6435052340778785</v>
+        <v>0.6493098863354534</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.94969175269443</v>
+        <v>15.73899948464483</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06885272674735961</v>
+        <v>0.06870979442177146</v>
       </c>
       <c r="C16">
-        <v>641.2932298686402</v>
+        <v>635.4178205475092</v>
       </c>
       <c r="D16">
-        <v>724.4872298686403</v>
+        <v>726.9328205475093</v>
       </c>
       <c r="E16">
-        <v>-353.506</v>
+        <v>-345.1849999999999</v>
       </c>
       <c r="F16">
-        <v>116.494</v>
+        <v>124.815</v>
       </c>
       <c r="G16">
         <v>33.3</v>
@@ -2599,28 +2599,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M16">
-        <v>5.859648200000001</v>
+        <v>6.278194500000001</v>
       </c>
       <c r="N16">
-        <v>86.3653518</v>
+        <v>85.9468055</v>
       </c>
       <c r="O16">
-        <v>21.53951873892</v>
+        <v>21.4351332917</v>
       </c>
       <c r="P16">
-        <v>64.82583306108</v>
+        <v>64.5116722083</v>
       </c>
       <c r="Q16">
-        <v>104.72583306108</v>
+        <v>104.4116722083</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07391511807832514</v>
+        <v>0.07417237343737819</v>
       </c>
       <c r="T16">
-        <v>0.6493098863354534</v>
+        <v>0.6552511186461475</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.73899948464483</v>
+        <v>14.68973285233517</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06870979442177146</v>
+        <v>0.0685668620961833</v>
       </c>
       <c r="C17">
-        <v>635.4178205475093</v>
+        <v>629.5589778991127</v>
       </c>
       <c r="D17">
-        <v>726.9328205475093</v>
+        <v>729.3949778991127</v>
       </c>
       <c r="E17">
-        <v>-345.185</v>
+        <v>-336.864</v>
       </c>
       <c r="F17">
-        <v>124.815</v>
+        <v>133.136</v>
       </c>
       <c r="G17">
         <v>33.3</v>
@@ -2681,28 +2681,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M17">
-        <v>6.2781945</v>
+        <v>6.6967408</v>
       </c>
       <c r="N17">
-        <v>85.9468055</v>
+        <v>85.52825919999999</v>
       </c>
       <c r="O17">
-        <v>21.4351332917</v>
+        <v>21.33074784448</v>
       </c>
       <c r="P17">
-        <v>64.5116722083</v>
+        <v>64.19751135551999</v>
       </c>
       <c r="Q17">
-        <v>104.4116722083</v>
+        <v>104.09751135552</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07417237343737819</v>
+        <v>0.07443575392402775</v>
       </c>
       <c r="T17">
-        <v>0.6552511186461475</v>
+        <v>0.6613338088690012</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.68973285233517</v>
+        <v>13.77162454906422</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0685668620961833</v>
+        <v>0.06842392977059517</v>
       </c>
       <c r="C18">
-        <v>629.5589778991127</v>
+        <v>623.7168708319672</v>
       </c>
       <c r="D18">
-        <v>729.3949778991127</v>
+        <v>731.8738708319672</v>
       </c>
       <c r="E18">
-        <v>-336.864</v>
+        <v>-328.543</v>
       </c>
       <c r="F18">
-        <v>133.136</v>
+        <v>141.457</v>
       </c>
       <c r="G18">
         <v>33.3</v>
@@ -2763,28 +2763,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M18">
-        <v>6.6967408</v>
+        <v>7.115287100000001</v>
       </c>
       <c r="N18">
-        <v>85.52825919999999</v>
+        <v>85.10971289999999</v>
       </c>
       <c r="O18">
-        <v>21.33074784448</v>
+        <v>21.22636239726</v>
       </c>
       <c r="P18">
-        <v>64.19751135551999</v>
+        <v>63.88335050273999</v>
       </c>
       <c r="Q18">
-        <v>104.09751135552</v>
+        <v>103.78335050274</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07443575392402775</v>
+        <v>0.07470548092842791</v>
       </c>
       <c r="T18">
-        <v>0.6613338088690012</v>
+        <v>0.6675630699405982</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.77162454906422</v>
+        <v>12.96152898735456</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06842392977059517</v>
+        <v>0.06848365944500701</v>
       </c>
       <c r="C19">
-        <v>623.7168708319672</v>
+        <v>614.3579252716977</v>
       </c>
       <c r="D19">
-        <v>731.8738708319672</v>
+        <v>730.8359252716978</v>
       </c>
       <c r="E19">
-        <v>-328.543</v>
+        <v>-320.222</v>
       </c>
       <c r="F19">
-        <v>141.457</v>
+        <v>149.778</v>
       </c>
       <c r="G19">
         <v>33.3</v>
@@ -2845,45 +2845,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M19">
-        <v>7.115287100000001</v>
+        <v>7.758500400000001</v>
       </c>
       <c r="N19">
-        <v>85.10971289999999</v>
+        <v>84.46649959999999</v>
       </c>
       <c r="O19">
-        <v>21.22636239726</v>
+        <v>21.06594500024</v>
       </c>
       <c r="P19">
-        <v>63.88335050273999</v>
+        <v>63.40055459975999</v>
       </c>
       <c r="Q19">
-        <v>103.78335050274</v>
+        <v>103.30055459976</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07470548092842791</v>
+        <v>0.07498178664025246</v>
       </c>
       <c r="T19">
-        <v>0.6675630699405982</v>
+        <v>0.6739442642090635</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.96152898735456</v>
+        <v>11.88696207323776</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06848365944500702</v>
+        <v>0.06835198611941885</v>
       </c>
       <c r="C20">
-        <v>614.3579252716975</v>
+        <v>608.3289842445738</v>
       </c>
       <c r="D20">
-        <v>730.8359252716975</v>
+        <v>733.1279842445739</v>
       </c>
       <c r="E20">
-        <v>-320.222</v>
+        <v>-311.901</v>
       </c>
       <c r="F20">
-        <v>149.778</v>
+        <v>158.099</v>
       </c>
       <c r="G20">
         <v>33.3</v>
@@ -2927,28 +2927,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M20">
-        <v>7.758500399999999</v>
+        <v>8.189528200000002</v>
       </c>
       <c r="N20">
-        <v>84.46649959999999</v>
+        <v>84.0354718</v>
       </c>
       <c r="O20">
-        <v>21.06594500024</v>
+        <v>20.95844666692</v>
       </c>
       <c r="P20">
-        <v>63.40055459975999</v>
+        <v>63.07702513308</v>
       </c>
       <c r="Q20">
-        <v>103.30055459976</v>
+        <v>102.97702513308</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07498178664025246</v>
+        <v>0.07526491471533192</v>
       </c>
       <c r="T20">
-        <v>0.6739442642090635</v>
+        <v>0.6804830188298365</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.88696207323776</v>
+        <v>11.26133249043577</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06835198611941885</v>
+        <v>0.06822031279383071</v>
       </c>
       <c r="C21">
-        <v>608.3289842445738</v>
+        <v>602.3144652298449</v>
       </c>
       <c r="D21">
-        <v>733.1279842445739</v>
+        <v>735.4344652298449</v>
       </c>
       <c r="E21">
-        <v>-311.901</v>
+        <v>-303.58</v>
       </c>
       <c r="F21">
-        <v>158.099</v>
+        <v>166.42</v>
       </c>
       <c r="G21">
         <v>33.3</v>
@@ -3009,28 +3009,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M21">
-        <v>8.189528200000002</v>
+        <v>8.620556000000001</v>
       </c>
       <c r="N21">
-        <v>84.0354718</v>
+        <v>83.604444</v>
       </c>
       <c r="O21">
-        <v>20.95844666692</v>
+        <v>20.8509483336</v>
       </c>
       <c r="P21">
-        <v>63.07702513308</v>
+        <v>62.7534956664</v>
       </c>
       <c r="Q21">
-        <v>102.97702513308</v>
+        <v>102.6534956664</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07526491471533192</v>
+        <v>0.07555512099228839</v>
       </c>
       <c r="T21">
-        <v>0.6804830188298365</v>
+        <v>0.687185242316129</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.26133249043577</v>
+        <v>10.69826586591399</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06822031279383071</v>
+        <v>0.06808863946824256</v>
       </c>
       <c r="C22">
-        <v>602.3144652298449</v>
+        <v>596.3145047756176</v>
       </c>
       <c r="D22">
-        <v>735.4344652298449</v>
+        <v>737.7555047756176</v>
       </c>
       <c r="E22">
-        <v>-303.58</v>
+        <v>-295.259</v>
       </c>
       <c r="F22">
-        <v>166.42</v>
+        <v>174.741</v>
       </c>
       <c r="G22">
         <v>33.3</v>
@@ -3091,28 +3091,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M22">
-        <v>8.620556000000001</v>
+        <v>9.051583800000001</v>
       </c>
       <c r="N22">
-        <v>83.604444</v>
+        <v>83.17341619999999</v>
       </c>
       <c r="O22">
-        <v>20.8509483336</v>
+        <v>20.74345000028</v>
       </c>
       <c r="P22">
-        <v>62.7534956664</v>
+        <v>62.42996619971999</v>
       </c>
       <c r="Q22">
-        <v>102.6534956664</v>
+        <v>102.32996619972</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07555512099228839</v>
+        <v>0.07585267426359818</v>
       </c>
       <c r="T22">
-        <v>0.687185242316129</v>
+        <v>0.6940571423463782</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.69826586591399</v>
+        <v>10.18882463420379</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06808863946824256</v>
+        <v>0.06823769054265441</v>
       </c>
       <c r="C23">
-        <v>596.3145047756176</v>
+        <v>585.3672336348194</v>
       </c>
       <c r="D23">
-        <v>737.7555047756176</v>
+        <v>735.1292336348195</v>
       </c>
       <c r="E23">
-        <v>-295.259</v>
+        <v>-286.938</v>
       </c>
       <c r="F23">
-        <v>174.741</v>
+        <v>183.062</v>
       </c>
       <c r="G23">
         <v>33.3</v>
@@ -3173,45 +3173,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M23">
-        <v>9.0515838</v>
+        <v>9.793817000000001</v>
       </c>
       <c r="N23">
-        <v>83.17341619999999</v>
+        <v>82.43118299999999</v>
       </c>
       <c r="O23">
-        <v>20.74345000028</v>
+        <v>20.5583370402</v>
       </c>
       <c r="P23">
-        <v>62.42996619971999</v>
+        <v>61.87284595979999</v>
       </c>
       <c r="Q23">
-        <v>102.32996619972</v>
+        <v>101.7728459598</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07585267426359818</v>
+        <v>0.07615785710596719</v>
       </c>
       <c r="T23">
-        <v>0.6940571423463782</v>
+        <v>0.7011052449415055</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.2494</v>
       </c>
       <c r="W23">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.1888246342038</v>
+        <v>9.416655426581892</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06823769054265441</v>
+        <v>0.06811877741706626</v>
       </c>
       <c r="C24">
-        <v>585.3672336348194</v>
+        <v>579.1399634654174</v>
       </c>
       <c r="D24">
-        <v>735.1292336348195</v>
+        <v>737.2229634654175</v>
       </c>
       <c r="E24">
-        <v>-286.938</v>
+        <v>-278.617</v>
       </c>
       <c r="F24">
-        <v>183.062</v>
+        <v>191.383</v>
       </c>
       <c r="G24">
         <v>33.3</v>
@@ -3255,28 +3255,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M24">
-        <v>9.793817000000001</v>
+        <v>10.2389905</v>
       </c>
       <c r="N24">
-        <v>82.43118299999999</v>
+        <v>81.98600949999999</v>
       </c>
       <c r="O24">
-        <v>20.5583370402</v>
+        <v>20.4473107693</v>
       </c>
       <c r="P24">
-        <v>61.87284595979999</v>
+        <v>61.53869873069999</v>
       </c>
       <c r="Q24">
-        <v>101.7728459598</v>
+        <v>101.4386987307</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07615785710596719</v>
+        <v>0.07647096677541072</v>
       </c>
       <c r="T24">
-        <v>0.7011052449415055</v>
+        <v>0.7083364151365062</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.416655426581892</v>
+        <v>9.007235625426159</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06811877741706626</v>
+        <v>0.0679998642914781</v>
       </c>
       <c r="C25">
-        <v>579.1399634654174</v>
+        <v>572.924653711523</v>
       </c>
       <c r="D25">
-        <v>737.2229634654175</v>
+        <v>739.3286537115231</v>
       </c>
       <c r="E25">
-        <v>-278.617</v>
+        <v>-270.296</v>
       </c>
       <c r="F25">
-        <v>191.383</v>
+        <v>199.704</v>
       </c>
       <c r="G25">
         <v>33.3</v>
@@ -3337,28 +3337,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M25">
-        <v>10.2389905</v>
+        <v>10.684164</v>
       </c>
       <c r="N25">
-        <v>81.98600949999999</v>
+        <v>81.540836</v>
       </c>
       <c r="O25">
-        <v>20.4473107693</v>
+        <v>20.3362844984</v>
       </c>
       <c r="P25">
-        <v>61.53869873069999</v>
+        <v>61.20455150159999</v>
       </c>
       <c r="Q25">
-        <v>101.4386987307</v>
+        <v>101.1045515016</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07647096677541072</v>
+        <v>0.0767923161729975</v>
       </c>
       <c r="T25">
-        <v>0.7083364151365062</v>
+        <v>0.7157578792840071</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.007235625426159</v>
+        <v>8.631934141033401</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0679998642914781</v>
+        <v>0.06788095116588995</v>
       </c>
       <c r="C26">
-        <v>572.924653711523</v>
+        <v>566.7214071523704</v>
       </c>
       <c r="D26">
-        <v>739.3286537115231</v>
+        <v>741.4464071523704</v>
       </c>
       <c r="E26">
-        <v>-270.296</v>
+        <v>-261.975</v>
       </c>
       <c r="F26">
-        <v>199.704</v>
+        <v>208.025</v>
       </c>
       <c r="G26">
         <v>33.3</v>
@@ -3419,28 +3419,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M26">
-        <v>10.684164</v>
+        <v>11.1293375</v>
       </c>
       <c r="N26">
-        <v>81.540836</v>
+        <v>81.09566249999999</v>
       </c>
       <c r="O26">
-        <v>20.3362844984</v>
+        <v>20.2252582275</v>
       </c>
       <c r="P26">
-        <v>61.20455150159999</v>
+        <v>60.87040427249999</v>
       </c>
       <c r="Q26">
-        <v>101.1045515016</v>
+        <v>100.7704042725</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0767923161729975</v>
+        <v>0.07712223488785327</v>
       </c>
       <c r="T26">
-        <v>0.7157578792840071</v>
+        <v>0.7233772491421079</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.631934141033401</v>
+        <v>8.286656775392064</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06788095116588995</v>
+        <v>0.06776203804030181</v>
       </c>
       <c r="C27">
-        <v>566.7214071523704</v>
+        <v>560.5303277481919</v>
       </c>
       <c r="D27">
-        <v>741.4464071523704</v>
+        <v>743.5763277481919</v>
       </c>
       <c r="E27">
-        <v>-261.975</v>
+        <v>-253.654</v>
       </c>
       <c r="F27">
-        <v>208.025</v>
+        <v>216.346</v>
       </c>
       <c r="G27">
         <v>33.3</v>
@@ -3501,28 +3501,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M27">
-        <v>11.1293375</v>
+        <v>11.574511</v>
       </c>
       <c r="N27">
-        <v>81.09566249999999</v>
+        <v>80.65048899999999</v>
       </c>
       <c r="O27">
-        <v>20.2252582275</v>
+        <v>20.1142319566</v>
       </c>
       <c r="P27">
-        <v>60.87040427249999</v>
+        <v>60.5362570434</v>
       </c>
       <c r="Q27">
-        <v>100.7704042725</v>
+        <v>100.4362570434</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07712223488785327</v>
+        <v>0.07746107032473218</v>
       </c>
       <c r="T27">
-        <v>0.7233772491421079</v>
+        <v>0.7312025479152925</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.286656775392064</v>
+        <v>7.967939207107756</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06776203804030181</v>
+        <v>0.06764312491471365</v>
       </c>
       <c r="C28">
-        <v>560.5303277481919</v>
+        <v>554.3515206572303</v>
       </c>
       <c r="D28">
-        <v>743.5763277481919</v>
+        <v>745.7185206572303</v>
       </c>
       <c r="E28">
-        <v>-253.654</v>
+        <v>-245.333</v>
       </c>
       <c r="F28">
-        <v>216.346</v>
+        <v>224.667</v>
       </c>
       <c r="G28">
         <v>33.3</v>
@@ -3583,28 +3583,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M28">
-        <v>11.574511</v>
+        <v>12.0196845</v>
       </c>
       <c r="N28">
-        <v>80.65048899999999</v>
+        <v>80.2053155</v>
       </c>
       <c r="O28">
-        <v>20.1142319566</v>
+        <v>20.0032056857</v>
       </c>
       <c r="P28">
-        <v>60.5362570434</v>
+        <v>60.2021098143</v>
       </c>
       <c r="Q28">
-        <v>100.4362570434</v>
+        <v>100.1021098143</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07746107032473218</v>
+        <v>0.07780918892426528</v>
       </c>
       <c r="T28">
-        <v>0.7312025479152925</v>
+        <v>0.7392422384356876</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.967939207107756</v>
+        <v>7.672830347585245</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06764312491471365</v>
+        <v>0.06769234618912551</v>
       </c>
       <c r="C29">
-        <v>554.3515206572303</v>
+        <v>545.1423152226362</v>
       </c>
       <c r="D29">
-        <v>745.7185206572303</v>
+        <v>744.8303152226363</v>
       </c>
       <c r="E29">
-        <v>-245.333</v>
+        <v>-237.012</v>
       </c>
       <c r="F29">
-        <v>224.667</v>
+        <v>232.988</v>
       </c>
       <c r="G29">
         <v>33.3</v>
@@ -3665,45 +3665,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M29">
-        <v>12.0196845</v>
+        <v>12.6512484</v>
       </c>
       <c r="N29">
-        <v>80.2053155</v>
+        <v>79.57375159999999</v>
       </c>
       <c r="O29">
-        <v>20.0032056857</v>
+        <v>19.84569364904</v>
       </c>
       <c r="P29">
-        <v>60.2021098143</v>
+        <v>59.72805795095999</v>
       </c>
       <c r="Q29">
-        <v>100.1021098143</v>
+        <v>99.62805795096</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07780918892426528</v>
+        <v>0.07816697748489654</v>
       </c>
       <c r="T29">
-        <v>0.7392422384356876</v>
+        <v>0.7475052536927606</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.672830347585245</v>
+        <v>7.289794420604371</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06769234618912551</v>
+        <v>0.06757943786353734</v>
       </c>
       <c r="C30">
-        <v>545.1423152226362</v>
+        <v>538.8619118055881</v>
       </c>
       <c r="D30">
-        <v>744.8303152226363</v>
+        <v>746.8709118055882</v>
       </c>
       <c r="E30">
-        <v>-237.012</v>
+        <v>-228.691</v>
       </c>
       <c r="F30">
-        <v>232.988</v>
+        <v>241.309</v>
       </c>
       <c r="G30">
         <v>33.3</v>
@@ -3747,28 +3747,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M30">
-        <v>12.6512484</v>
+        <v>13.1030787</v>
       </c>
       <c r="N30">
-        <v>79.57375159999999</v>
+        <v>79.1219213</v>
       </c>
       <c r="O30">
-        <v>19.84569364904</v>
+        <v>19.73300717222</v>
       </c>
       <c r="P30">
-        <v>59.72805795095999</v>
+        <v>59.38891412778</v>
       </c>
       <c r="Q30">
-        <v>99.62805795096</v>
+        <v>99.28891412778</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07816697748489654</v>
+        <v>0.07853484459653148</v>
       </c>
       <c r="T30">
-        <v>0.7475052536927606</v>
+        <v>0.7560010299429903</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.289794420604371</v>
+        <v>7.038422199204222</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06757943786353734</v>
+        <v>0.0674665295379492</v>
       </c>
       <c r="C31">
-        <v>538.8619118055882</v>
+        <v>532.5927202680527</v>
       </c>
       <c r="D31">
-        <v>746.8709118055882</v>
+        <v>748.9227202680528</v>
       </c>
       <c r="E31">
-        <v>-228.691</v>
+        <v>-220.37</v>
       </c>
       <c r="F31">
-        <v>241.309</v>
+        <v>249.63</v>
       </c>
       <c r="G31">
         <v>33.3</v>
@@ -3829,28 +3829,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M31">
-        <v>13.1030787</v>
+        <v>13.554909</v>
       </c>
       <c r="N31">
-        <v>79.1219213</v>
+        <v>78.670091</v>
       </c>
       <c r="O31">
-        <v>19.73300717222</v>
+        <v>19.6203206954</v>
       </c>
       <c r="P31">
-        <v>59.38891412778</v>
+        <v>59.0497703046</v>
       </c>
       <c r="Q31">
-        <v>99.28891412778</v>
+        <v>98.94977030460001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07853484459653148</v>
+        <v>0.0789132221970703</v>
       </c>
       <c r="T31">
-        <v>0.7560010299429902</v>
+        <v>0.7647395426575124</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.038422199204223</v>
+        <v>6.803808125897414</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0674665295379492</v>
+        <v>0.06735362121236105</v>
       </c>
       <c r="C32">
-        <v>532.5927202680527</v>
+        <v>526.3348332686197</v>
       </c>
       <c r="D32">
-        <v>748.9227202680528</v>
+        <v>750.9858332686198</v>
       </c>
       <c r="E32">
-        <v>-220.37</v>
+        <v>-212.049</v>
       </c>
       <c r="F32">
-        <v>249.63</v>
+        <v>257.951</v>
       </c>
       <c r="G32">
         <v>33.3</v>
@@ -3911,28 +3911,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M32">
-        <v>13.554909</v>
+        <v>14.0067393</v>
       </c>
       <c r="N32">
-        <v>78.670091</v>
+        <v>78.21826069999999</v>
       </c>
       <c r="O32">
-        <v>19.6203206954</v>
+        <v>19.50763421858</v>
       </c>
       <c r="P32">
-        <v>59.0497703046</v>
+        <v>58.71062648141999</v>
       </c>
       <c r="Q32">
-        <v>98.94977030460001</v>
+        <v>98.61062648141998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0789132221970703</v>
+        <v>0.07930256726429138</v>
       </c>
       <c r="T32">
-        <v>0.7647395426575124</v>
+        <v>0.7737313455956438</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.803808125897414</v>
+        <v>6.584330444416851</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06735362121236105</v>
+        <v>0.0672407128867729</v>
       </c>
       <c r="C33">
-        <v>526.3348332686197</v>
+        <v>520.0883444897136</v>
       </c>
       <c r="D33">
-        <v>750.9858332686198</v>
+        <v>753.0603444897137</v>
       </c>
       <c r="E33">
-        <v>-212.049</v>
+        <v>-203.728</v>
       </c>
       <c r="F33">
-        <v>257.951</v>
+        <v>266.272</v>
       </c>
       <c r="G33">
         <v>33.3</v>
@@ -3993,28 +3993,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M33">
-        <v>14.0067393</v>
+        <v>14.4585696</v>
       </c>
       <c r="N33">
-        <v>78.21826069999999</v>
+        <v>77.76643039999999</v>
       </c>
       <c r="O33">
-        <v>19.50763421858</v>
+        <v>19.39494774176</v>
       </c>
       <c r="P33">
-        <v>58.71062648141999</v>
+        <v>58.37148265823999</v>
       </c>
       <c r="Q33">
-        <v>98.61062648141998</v>
+        <v>98.27148265823999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07930256726429138</v>
+        <v>0.07970336365701897</v>
       </c>
       <c r="T33">
-        <v>0.7737313455956438</v>
+        <v>0.7829876133260731</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.584330444416851</v>
+        <v>6.378570118028826</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0672407128867729</v>
+        <v>0.06712780456118475</v>
       </c>
       <c r="C34">
-        <v>520.0883444897136</v>
+        <v>513.8533486517731</v>
       </c>
       <c r="D34">
-        <v>753.0603444897137</v>
+        <v>755.1463486517732</v>
       </c>
       <c r="E34">
-        <v>-203.728</v>
+        <v>-195.407</v>
       </c>
       <c r="F34">
-        <v>266.272</v>
+        <v>274.593</v>
       </c>
       <c r="G34">
         <v>33.3</v>
@@ -4075,28 +4075,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M34">
-        <v>14.4585696</v>
+        <v>14.9103999</v>
       </c>
       <c r="N34">
-        <v>77.76643039999999</v>
+        <v>77.31460009999999</v>
       </c>
       <c r="O34">
-        <v>19.39494774176</v>
+        <v>19.28226126494</v>
       </c>
       <c r="P34">
-        <v>58.37148265823999</v>
+        <v>58.03233883505999</v>
       </c>
       <c r="Q34">
-        <v>98.27148265823999</v>
+        <v>97.93233883505999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07970336365701897</v>
+        <v>0.08011612412117128</v>
       </c>
       <c r="T34">
-        <v>0.7829876133260731</v>
+        <v>0.7925201875559184</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.378570118028826</v>
+        <v>6.185280114452194</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06712780456118475</v>
+        <v>0.06727010023559658</v>
       </c>
       <c r="C35">
-        <v>513.8533486517731</v>
+        <v>502.9052960792572</v>
       </c>
       <c r="D35">
-        <v>755.1463486517732</v>
+        <v>752.5192960792573</v>
       </c>
       <c r="E35">
-        <v>-195.407</v>
+        <v>-187.086</v>
       </c>
       <c r="F35">
-        <v>274.593</v>
+        <v>282.914</v>
       </c>
       <c r="G35">
         <v>33.3</v>
@@ -4157,45 +4157,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M35">
-        <v>14.9103999</v>
+        <v>15.6451442</v>
       </c>
       <c r="N35">
-        <v>77.31460009999999</v>
+        <v>76.57985579999999</v>
       </c>
       <c r="O35">
-        <v>19.28226126494</v>
+        <v>19.09901603652</v>
       </c>
       <c r="P35">
-        <v>58.03233883505999</v>
+        <v>57.48083976347999</v>
       </c>
       <c r="Q35">
-        <v>97.93233883505999</v>
+        <v>97.38083976348</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08011612412117128</v>
+        <v>0.08054139247817665</v>
       </c>
       <c r="T35">
-        <v>0.7925201875559184</v>
+        <v>0.8023416276715164</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.2494</v>
       </c>
       <c r="W35">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.185280114452194</v>
+        <v>5.894800253742626</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06727010023559658</v>
+        <v>0.06716469791000844</v>
       </c>
       <c r="C36">
-        <v>502.9052960792572</v>
+        <v>496.5284665691655</v>
       </c>
       <c r="D36">
-        <v>752.5192960792573</v>
+        <v>754.4634665691656</v>
       </c>
       <c r="E36">
-        <v>-187.086</v>
+        <v>-178.765</v>
       </c>
       <c r="F36">
-        <v>282.914</v>
+        <v>291.235</v>
       </c>
       <c r="G36">
         <v>33.3</v>
@@ -4239,28 +4239,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M36">
-        <v>15.6451442</v>
+        <v>16.1052955</v>
       </c>
       <c r="N36">
-        <v>76.57985579999999</v>
+        <v>76.1197045</v>
       </c>
       <c r="O36">
-        <v>19.09901603652</v>
+        <v>18.9842543023</v>
       </c>
       <c r="P36">
-        <v>57.48083976347999</v>
+        <v>57.1354501977</v>
       </c>
       <c r="Q36">
-        <v>97.38083976348</v>
+        <v>97.03545019769999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08054139247817665</v>
+        <v>0.08097974601539762</v>
       </c>
       <c r="T36">
-        <v>0.8023416276715164</v>
+        <v>0.8124652659445175</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.894800253742626</v>
+        <v>5.726377389349981</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06716469791000844</v>
+        <v>0.06705929558442029</v>
       </c>
       <c r="C37">
-        <v>496.5284665691655</v>
+        <v>490.1617087994363</v>
       </c>
       <c r="D37">
-        <v>754.4634665691656</v>
+        <v>756.4177087994364</v>
       </c>
       <c r="E37">
-        <v>-178.765</v>
+        <v>-170.444</v>
       </c>
       <c r="F37">
-        <v>291.235</v>
+        <v>299.556</v>
       </c>
       <c r="G37">
         <v>33.3</v>
@@ -4321,28 +4321,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M37">
-        <v>16.1052955</v>
+        <v>16.5654468</v>
       </c>
       <c r="N37">
-        <v>76.1197045</v>
+        <v>75.65955319999999</v>
       </c>
       <c r="O37">
-        <v>18.9842543023</v>
+        <v>18.86949256808</v>
       </c>
       <c r="P37">
-        <v>57.1354501977</v>
+        <v>56.79006063191999</v>
       </c>
       <c r="Q37">
-        <v>97.03545019769999</v>
+        <v>96.69006063191999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08097974601539762</v>
+        <v>0.08143179810065672</v>
       </c>
       <c r="T37">
-        <v>0.8124652659445175</v>
+        <v>0.82290526791355</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.726377389349981</v>
+        <v>5.567311350756925</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06705929558442029</v>
+        <v>0.06695389325883215</v>
       </c>
       <c r="C38">
-        <v>490.1617087994363</v>
+        <v>483.8051012380265</v>
       </c>
       <c r="D38">
-        <v>756.4177087994364</v>
+        <v>758.3821012380265</v>
       </c>
       <c r="E38">
-        <v>-170.444</v>
+        <v>-162.123</v>
       </c>
       <c r="F38">
-        <v>299.556</v>
+        <v>307.877</v>
       </c>
       <c r="G38">
         <v>33.3</v>
@@ -4403,28 +4403,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M38">
-        <v>16.5654468</v>
+        <v>17.0255981</v>
       </c>
       <c r="N38">
-        <v>75.65955319999999</v>
+        <v>75.1994019</v>
       </c>
       <c r="O38">
-        <v>18.86949256808</v>
+        <v>18.75473083386</v>
       </c>
       <c r="P38">
-        <v>56.79006063191999</v>
+        <v>56.44467106614</v>
       </c>
       <c r="Q38">
-        <v>96.69006063191999</v>
+        <v>96.34467106613999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08143179810065672</v>
+        <v>0.08189820104576531</v>
       </c>
       <c r="T38">
-        <v>0.82290526791355</v>
+        <v>0.8336766985165198</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.567311350756926</v>
+        <v>5.416843476412144</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06695389325883215</v>
+        <v>0.06684849093324399</v>
       </c>
       <c r="C39">
-        <v>483.8051012380265</v>
+        <v>477.4587231701296</v>
       </c>
       <c r="D39">
-        <v>758.3821012380265</v>
+        <v>760.3567231701297</v>
       </c>
       <c r="E39">
-        <v>-162.123</v>
+        <v>-153.802</v>
       </c>
       <c r="F39">
-        <v>307.877</v>
+        <v>316.198</v>
       </c>
       <c r="G39">
         <v>33.3</v>
@@ -4485,28 +4485,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M39">
-        <v>17.0255981</v>
+        <v>17.4857494</v>
       </c>
       <c r="N39">
-        <v>75.1994019</v>
+        <v>74.73925059999999</v>
       </c>
       <c r="O39">
-        <v>18.75473083386</v>
+        <v>18.63996909964</v>
       </c>
       <c r="P39">
-        <v>56.44467106614</v>
+        <v>56.09928150035999</v>
       </c>
       <c r="Q39">
-        <v>96.34467106613999</v>
+        <v>95.99928150035998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08189820104576531</v>
+        <v>0.08237964924716773</v>
       </c>
       <c r="T39">
-        <v>0.8336766985165198</v>
+        <v>0.8447955946228113</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.416843476412144</v>
+        <v>5.274294963874981</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06684849093324399</v>
+        <v>0.06674308860765585</v>
       </c>
       <c r="C40">
-        <v>477.4587231701296</v>
+        <v>471.122654708844</v>
       </c>
       <c r="D40">
-        <v>760.3567231701297</v>
+        <v>762.3416547088441</v>
       </c>
       <c r="E40">
-        <v>-153.802</v>
+        <v>-145.481</v>
       </c>
       <c r="F40">
-        <v>316.198</v>
+        <v>324.519</v>
       </c>
       <c r="G40">
         <v>33.3</v>
@@ -4567,28 +4567,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M40">
-        <v>17.4857494</v>
+        <v>17.9459007</v>
       </c>
       <c r="N40">
-        <v>74.73925059999999</v>
+        <v>74.2790993</v>
       </c>
       <c r="O40">
-        <v>18.63996909964</v>
+        <v>18.52520736542</v>
       </c>
       <c r="P40">
-        <v>56.09928150035999</v>
+        <v>55.75389193458</v>
       </c>
       <c r="Q40">
-        <v>95.99928150035998</v>
+        <v>95.65389193458</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08237964924716773</v>
+        <v>0.08287688263550139</v>
       </c>
       <c r="T40">
-        <v>0.8447955946228113</v>
+        <v>0.856279044699801</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.274294963874981</v>
+        <v>5.139056631467932</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06674308860765585</v>
+        <v>0.06663768628206769</v>
       </c>
       <c r="C41">
-        <v>471.122654708844</v>
+        <v>464.7969768060074</v>
       </c>
       <c r="D41">
-        <v>762.3416547088441</v>
+        <v>764.3369768060074</v>
       </c>
       <c r="E41">
-        <v>-145.481</v>
+        <v>-137.16</v>
       </c>
       <c r="F41">
-        <v>324.519</v>
+        <v>332.84</v>
       </c>
       <c r="G41">
         <v>33.3</v>
@@ -4649,28 +4649,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M41">
-        <v>17.9459007</v>
+        <v>18.406052</v>
       </c>
       <c r="N41">
-        <v>74.2790993</v>
+        <v>73.81894799999999</v>
       </c>
       <c r="O41">
-        <v>18.52520736542</v>
+        <v>18.4104456312</v>
       </c>
       <c r="P41">
-        <v>55.75389193458</v>
+        <v>55.40850236879999</v>
       </c>
       <c r="Q41">
-        <v>95.65389193458</v>
+        <v>95.30850236879999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08287688263550139</v>
+        <v>0.08339069047011283</v>
       </c>
       <c r="T41">
-        <v>0.856279044699801</v>
+        <v>0.8681452764460236</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.139056631467932</v>
+        <v>5.010580215681233</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06663768628206769</v>
+        <v>0.06653228395647955</v>
       </c>
       <c r="C42">
-        <v>464.7969768060074</v>
+        <v>458.4817712632007</v>
       </c>
       <c r="D42">
-        <v>764.3369768060074</v>
+        <v>766.3427712632008</v>
       </c>
       <c r="E42">
-        <v>-137.16</v>
+        <v>-128.8389999999999</v>
       </c>
       <c r="F42">
-        <v>332.84</v>
+        <v>341.1610000000001</v>
       </c>
       <c r="G42">
         <v>33.3</v>
@@ -4731,28 +4731,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M42">
-        <v>18.406052</v>
+        <v>18.8662033</v>
       </c>
       <c r="N42">
-        <v>73.81894799999999</v>
+        <v>73.3587967</v>
       </c>
       <c r="O42">
-        <v>18.4104456312</v>
+        <v>18.29568389698</v>
       </c>
       <c r="P42">
-        <v>55.40850236879999</v>
+        <v>55.06311280302</v>
       </c>
       <c r="Q42">
-        <v>95.30850236879999</v>
+        <v>94.96311280302</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08339069047011283</v>
+        <v>0.08392191551945685</v>
       </c>
       <c r="T42">
-        <v>0.8681452764460236</v>
+        <v>0.880413753336186</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.010580215681233</v>
+        <v>4.888370942128033</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06653228395647955</v>
+        <v>0.06642688163089139</v>
       </c>
       <c r="C43">
-        <v>458.4817712632007</v>
+        <v>452.1771207429296</v>
       </c>
       <c r="D43">
-        <v>766.3427712632008</v>
+        <v>768.3591207429297</v>
       </c>
       <c r="E43">
-        <v>-128.8389999999999</v>
+        <v>-120.518</v>
       </c>
       <c r="F43">
-        <v>341.1610000000001</v>
+        <v>349.482</v>
       </c>
       <c r="G43">
         <v>33.3</v>
@@ -4813,28 +4813,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M43">
-        <v>18.8662033</v>
+        <v>19.3263546</v>
       </c>
       <c r="N43">
-        <v>73.3587967</v>
+        <v>72.89864539999999</v>
       </c>
       <c r="O43">
-        <v>18.29568389698</v>
+        <v>18.18092216276</v>
       </c>
       <c r="P43">
-        <v>55.06311280302</v>
+        <v>54.71772323723999</v>
       </c>
       <c r="Q43">
-        <v>94.96311280302</v>
+        <v>94.61772323724</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08392191551945685</v>
+        <v>0.08447145867395067</v>
       </c>
       <c r="T43">
-        <v>0.880413753336186</v>
+        <v>0.8931052811535952</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.888370942128033</v>
+        <v>4.77198115779165</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06642688163089139</v>
+        <v>0.06632147930530324</v>
       </c>
       <c r="C44">
-        <v>452.1771207429297</v>
+        <v>445.8831087799775</v>
       </c>
       <c r="D44">
-        <v>768.3591207429297</v>
+        <v>770.3861087799776</v>
       </c>
       <c r="E44">
-        <v>-120.518</v>
+        <v>-112.197</v>
       </c>
       <c r="F44">
-        <v>349.482</v>
+        <v>357.803</v>
       </c>
       <c r="G44">
         <v>33.3</v>
@@ -4895,28 +4895,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M44">
-        <v>19.3263546</v>
+        <v>19.7865059</v>
       </c>
       <c r="N44">
-        <v>72.89864539999999</v>
+        <v>72.43849409999999</v>
       </c>
       <c r="O44">
-        <v>18.18092216276</v>
+        <v>18.06616042854</v>
       </c>
       <c r="P44">
-        <v>54.71772323723999</v>
+        <v>54.37233367145998</v>
       </c>
       <c r="Q44">
-        <v>94.61772323724</v>
+        <v>94.27233367145999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08447145867395067</v>
+        <v>0.08504028404439165</v>
       </c>
       <c r="T44">
-        <v>0.8931052811535951</v>
+        <v>0.9062421257365275</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.771981157791651</v>
+        <v>4.661004851796495</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06632147930530324</v>
+        <v>0.0662160769797151</v>
       </c>
       <c r="C45">
-        <v>445.8831087799775</v>
+        <v>439.599819792944</v>
       </c>
       <c r="D45">
-        <v>770.3861087799776</v>
+        <v>772.4238197929441</v>
       </c>
       <c r="E45">
-        <v>-112.197</v>
+        <v>-103.876</v>
       </c>
       <c r="F45">
-        <v>357.803</v>
+        <v>366.124</v>
       </c>
       <c r="G45">
         <v>33.3</v>
@@ -4977,28 +4977,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M45">
-        <v>19.7865059</v>
+        <v>20.2466572</v>
       </c>
       <c r="N45">
-        <v>72.43849409999999</v>
+        <v>71.97834279999999</v>
       </c>
       <c r="O45">
-        <v>18.06616042854</v>
+        <v>17.95139869432</v>
       </c>
       <c r="P45">
-        <v>54.37233367145998</v>
+        <v>54.02694410567999</v>
       </c>
       <c r="Q45">
-        <v>94.27233367145999</v>
+        <v>93.92694410567999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08504028404439165</v>
+        <v>0.08562942460663409</v>
       </c>
       <c r="T45">
-        <v>0.9062421257365275</v>
+        <v>0.9198481433402791</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.661004851796495</v>
+        <v>4.555072923346575</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0662160769797151</v>
+        <v>0.06695509965412694</v>
       </c>
       <c r="C46">
-        <v>439.599819792944</v>
+        <v>417.2145598230977</v>
       </c>
       <c r="D46">
-        <v>772.4238197929441</v>
+        <v>758.3595598230977</v>
       </c>
       <c r="E46">
-        <v>-103.876</v>
+        <v>-95.55500000000001</v>
       </c>
       <c r="F46">
-        <v>366.124</v>
+        <v>374.445</v>
       </c>
       <c r="G46">
         <v>33.3</v>
@@ -5059,45 +5059,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M46">
-        <v>20.2466572</v>
+        <v>21.642921</v>
       </c>
       <c r="N46">
-        <v>71.97834279999999</v>
+        <v>70.58207899999999</v>
       </c>
       <c r="O46">
-        <v>17.95139869432</v>
+        <v>17.6031705026</v>
       </c>
       <c r="P46">
-        <v>54.02694410567999</v>
+        <v>52.9789084974</v>
       </c>
       <c r="Q46">
-        <v>93.92694410567999</v>
+        <v>92.8789084974</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08562942460663409</v>
+        <v>0.08623998846204897</v>
       </c>
       <c r="T46">
-        <v>0.9198481433402791</v>
+        <v>0.9339489252205306</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.2494</v>
       </c>
       <c r="W46">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.555072923346575</v>
+        <v>4.26120854943748</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06695509965412694</v>
+        <v>0.0668684623285388</v>
       </c>
       <c r="C47">
-        <v>417.2145598230977</v>
+        <v>410.5157870500136</v>
       </c>
       <c r="D47">
-        <v>758.3595598230977</v>
+        <v>759.9817870500136</v>
       </c>
       <c r="E47">
-        <v>-95.55500000000001</v>
+        <v>-87.23399999999998</v>
       </c>
       <c r="F47">
-        <v>374.445</v>
+        <v>382.766</v>
       </c>
       <c r="G47">
         <v>33.3</v>
@@ -5141,28 +5141,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M47">
-        <v>21.642921</v>
+        <v>22.1238748</v>
       </c>
       <c r="N47">
-        <v>70.58207899999999</v>
+        <v>70.10112519999998</v>
       </c>
       <c r="O47">
-        <v>17.6031705026</v>
+        <v>17.48322062488</v>
       </c>
       <c r="P47">
-        <v>52.9789084974</v>
+        <v>52.61790457511999</v>
       </c>
       <c r="Q47">
-        <v>92.8789084974</v>
+        <v>92.51790457511999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08623998846204897</v>
+        <v>0.08687316579359036</v>
       </c>
       <c r="T47">
-        <v>0.9339489252205306</v>
+        <v>0.9485719582815323</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.26120854943748</v>
+        <v>4.168573580971447</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0668684623285388</v>
+        <v>0.06678182500295066</v>
       </c>
       <c r="C48">
-        <v>410.5157870500136</v>
+        <v>403.823969454274</v>
       </c>
       <c r="D48">
-        <v>759.9817870500136</v>
+        <v>761.6109694542741</v>
       </c>
       <c r="E48">
-        <v>-87.23399999999998</v>
+        <v>-78.91299999999995</v>
       </c>
       <c r="F48">
-        <v>382.766</v>
+        <v>391.087</v>
       </c>
       <c r="G48">
         <v>33.3</v>
@@ -5223,28 +5223,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M48">
-        <v>22.1238748</v>
+        <v>22.6048286</v>
       </c>
       <c r="N48">
-        <v>70.10112519999998</v>
+        <v>69.62017139999999</v>
       </c>
       <c r="O48">
-        <v>17.48322062488</v>
+        <v>17.36327074716</v>
       </c>
       <c r="P48">
-        <v>52.61790457511999</v>
+        <v>52.25690065283999</v>
       </c>
       <c r="Q48">
-        <v>92.51790457511999</v>
+        <v>92.15690065283999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08687316579359036</v>
+        <v>0.08753023660934084</v>
       </c>
       <c r="T48">
-        <v>0.9485719582815323</v>
+        <v>0.9637468039108735</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.168573580971447</v>
+        <v>4.079880526057162</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06678182500295066</v>
+        <v>0.06795619567736248</v>
       </c>
       <c r="C49">
-        <v>403.823969454274</v>
+        <v>373.9969518694644</v>
       </c>
       <c r="D49">
-        <v>761.6109694542741</v>
+        <v>740.1049518694645</v>
       </c>
       <c r="E49">
-        <v>-78.91299999999995</v>
+        <v>-70.59199999999998</v>
       </c>
       <c r="F49">
-        <v>391.087</v>
+        <v>399.408</v>
       </c>
       <c r="G49">
         <v>33.3</v>
@@ -5305,45 +5305,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M49">
-        <v>22.6048286</v>
+        <v>24.4837104</v>
       </c>
       <c r="N49">
-        <v>69.62017139999999</v>
+        <v>67.74128959999999</v>
       </c>
       <c r="O49">
-        <v>17.36327074716</v>
+        <v>16.89467762624</v>
       </c>
       <c r="P49">
-        <v>52.25690065283999</v>
+        <v>50.84661197375999</v>
       </c>
       <c r="Q49">
-        <v>92.15690065283999</v>
+        <v>90.74661197376</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08753023660934084</v>
+        <v>0.08821257937954324</v>
       </c>
       <c r="T49">
-        <v>0.9637468039108735</v>
+        <v>0.9795052974490356</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.2494</v>
       </c>
       <c r="W49">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.079880526057162</v>
+        <v>3.766790183893042</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06795619567736248</v>
+        <v>0.06789582935177434</v>
       </c>
       <c r="C50">
-        <v>373.9969518694644</v>
+        <v>366.7517740533432</v>
       </c>
       <c r="D50">
-        <v>740.1049518694645</v>
+        <v>741.1807740533433</v>
       </c>
       <c r="E50">
-        <v>-70.59199999999998</v>
+        <v>-62.27100000000002</v>
       </c>
       <c r="F50">
-        <v>399.408</v>
+        <v>407.729</v>
       </c>
       <c r="G50">
         <v>33.3</v>
@@ -5387,28 +5387,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M50">
-        <v>24.4837104</v>
+        <v>24.9937877</v>
       </c>
       <c r="N50">
-        <v>67.74128959999999</v>
+        <v>67.2312123</v>
       </c>
       <c r="O50">
-        <v>16.89467762624</v>
+        <v>16.76746434762</v>
       </c>
       <c r="P50">
-        <v>50.84661197375999</v>
+        <v>50.46374795238</v>
       </c>
       <c r="Q50">
-        <v>90.74661197376</v>
+        <v>90.36374795238</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08821257937954324</v>
+        <v>0.0889216806897536</v>
       </c>
       <c r="T50">
-        <v>0.9795052974490355</v>
+        <v>0.9958817711259491</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.766790183893042</v>
+        <v>3.689916914834001</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06789582935177434</v>
+        <v>0.06783546302618619</v>
       </c>
       <c r="C51">
-        <v>366.7517740533432</v>
+        <v>359.5097284368198</v>
       </c>
       <c r="D51">
-        <v>741.1807740533433</v>
+        <v>742.2597284368198</v>
       </c>
       <c r="E51">
-        <v>-62.27100000000002</v>
+        <v>-53.94999999999999</v>
       </c>
       <c r="F51">
-        <v>407.729</v>
+        <v>416.05</v>
       </c>
       <c r="G51">
         <v>33.3</v>
@@ -5469,28 +5469,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M51">
-        <v>24.9937877</v>
+        <v>25.503865</v>
       </c>
       <c r="N51">
-        <v>67.2312123</v>
+        <v>66.72113499999999</v>
       </c>
       <c r="O51">
-        <v>16.76746434762</v>
+        <v>16.640251069</v>
       </c>
       <c r="P51">
-        <v>50.46374795238</v>
+        <v>50.08088393099999</v>
       </c>
       <c r="Q51">
-        <v>90.36374795238</v>
+        <v>89.98088393099999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0889216806897536</v>
+        <v>0.08965914605237238</v>
       </c>
       <c r="T51">
-        <v>0.9958817711259491</v>
+        <v>1.012913303749939</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.689916914834001</v>
+        <v>3.61611857653732</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06783546302618619</v>
+        <v>0.06777509670059803</v>
       </c>
       <c r="C52">
-        <v>359.5097284368198</v>
+        <v>352.2708287186871</v>
       </c>
       <c r="D52">
-        <v>742.2597284368198</v>
+        <v>743.3418287186872</v>
       </c>
       <c r="E52">
-        <v>-53.94999999999999</v>
+        <v>-45.62899999999996</v>
       </c>
       <c r="F52">
-        <v>416.05</v>
+        <v>424.371</v>
       </c>
       <c r="G52">
         <v>33.3</v>
@@ -5551,28 +5551,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M52">
-        <v>25.503865</v>
+        <v>26.0139423</v>
       </c>
       <c r="N52">
-        <v>66.72113499999999</v>
+        <v>66.2110577</v>
       </c>
       <c r="O52">
-        <v>16.640251069</v>
+        <v>16.51303779038</v>
       </c>
       <c r="P52">
-        <v>50.08088393099999</v>
+        <v>49.69801990962</v>
       </c>
       <c r="Q52">
-        <v>89.98088393099999</v>
+        <v>89.59801990962001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08965914605237238</v>
+        <v>0.09042671204203681</v>
       </c>
       <c r="T52">
-        <v>1.012913303749939</v>
+        <v>1.030640000970827</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.61611857653732</v>
+        <v>3.545214290722863</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06777509670059803</v>
+        <v>0.06880760397500989</v>
       </c>
       <c r="C53">
-        <v>352.2708287186871</v>
+        <v>325.8655070646502</v>
       </c>
       <c r="D53">
-        <v>743.3418287186872</v>
+        <v>725.2575070646502</v>
       </c>
       <c r="E53">
-        <v>-45.62899999999996</v>
+        <v>-37.30799999999999</v>
       </c>
       <c r="F53">
-        <v>424.371</v>
+        <v>432.692</v>
       </c>
       <c r="G53">
         <v>33.3</v>
@@ -5633,45 +5633,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M53">
-        <v>26.0139423</v>
+        <v>27.7355572</v>
       </c>
       <c r="N53">
-        <v>66.2110577</v>
+        <v>64.48944279999999</v>
       </c>
       <c r="O53">
-        <v>16.51303779038</v>
+        <v>16.08366703432</v>
       </c>
       <c r="P53">
-        <v>49.69801990962</v>
+        <v>48.40577576567999</v>
       </c>
       <c r="Q53">
-        <v>89.59801990962001</v>
+        <v>88.30577576567998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09042671204203681</v>
+        <v>0.09122625994793726</v>
       </c>
       <c r="T53">
-        <v>1.030640000970827</v>
+        <v>1.049105310575918</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.2494</v>
       </c>
       <c r="W53">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.545214290722863</v>
+        <v>3.325154037287557</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06880760397500989</v>
+        <v>0.06876825444942172</v>
       </c>
       <c r="C54">
-        <v>325.8655070646502</v>
+        <v>318.2175691346494</v>
       </c>
       <c r="D54">
-        <v>725.2575070646502</v>
+        <v>725.9305691346494</v>
       </c>
       <c r="E54">
-        <v>-37.30799999999999</v>
+        <v>-28.98699999999997</v>
       </c>
       <c r="F54">
-        <v>432.692</v>
+        <v>441.013</v>
       </c>
       <c r="G54">
         <v>33.3</v>
@@ -5715,28 +5715,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M54">
-        <v>27.7355572</v>
+        <v>28.2689333</v>
       </c>
       <c r="N54">
-        <v>64.48944279999999</v>
+        <v>63.95606669999999</v>
       </c>
       <c r="O54">
-        <v>16.08366703432</v>
+        <v>15.95064303498</v>
       </c>
       <c r="P54">
-        <v>48.40577576567999</v>
+        <v>48.00542366502</v>
       </c>
       <c r="Q54">
-        <v>88.30577576567998</v>
+        <v>87.90542366502</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09122625994793726</v>
+        <v>0.09205983116898242</v>
       </c>
       <c r="T54">
-        <v>1.049105310575918</v>
+        <v>1.068356378036545</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.325154037287557</v>
+        <v>3.262415281867038</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06876825444942172</v>
+        <v>0.06872890492383357</v>
       </c>
       <c r="C55">
-        <v>318.2175691346494</v>
+        <v>310.5708816111487</v>
       </c>
       <c r="D55">
-        <v>725.9305691346494</v>
+        <v>726.6048816111488</v>
       </c>
       <c r="E55">
-        <v>-28.98699999999997</v>
+        <v>-20.66599999999994</v>
       </c>
       <c r="F55">
-        <v>441.013</v>
+        <v>449.3340000000001</v>
       </c>
       <c r="G55">
         <v>33.3</v>
@@ -5797,28 +5797,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M55">
-        <v>28.2689333</v>
+        <v>28.80230940000001</v>
       </c>
       <c r="N55">
-        <v>63.95606669999999</v>
+        <v>63.42269059999999</v>
       </c>
       <c r="O55">
-        <v>15.95064303498</v>
+        <v>15.81761903564</v>
       </c>
       <c r="P55">
-        <v>48.00542366502</v>
+        <v>47.60507156435999</v>
       </c>
       <c r="Q55">
-        <v>87.90542366502</v>
+        <v>87.50507156435998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09205983116898242</v>
+        <v>0.09292964461702953</v>
       </c>
       <c r="T55">
-        <v>1.068356378036545</v>
+        <v>1.088444448430243</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.262415281867038</v>
+        <v>3.202000184054685</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06872890492383357</v>
+        <v>0.06868955539824542</v>
       </c>
       <c r="C56">
-        <v>310.5708816111487</v>
+        <v>302.9254479818733</v>
       </c>
       <c r="D56">
-        <v>726.6048816111488</v>
+        <v>727.2804479818734</v>
       </c>
       <c r="E56">
-        <v>-20.66599999999994</v>
+        <v>-12.34499999999997</v>
       </c>
       <c r="F56">
-        <v>449.3340000000001</v>
+        <v>457.655</v>
       </c>
       <c r="G56">
         <v>33.3</v>
@@ -5879,28 +5879,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M56">
-        <v>28.80230940000001</v>
+        <v>29.3356855</v>
       </c>
       <c r="N56">
-        <v>63.42269059999999</v>
+        <v>62.88931449999999</v>
       </c>
       <c r="O56">
-        <v>15.81761903564</v>
+        <v>15.6845950363</v>
       </c>
       <c r="P56">
-        <v>47.60507156435999</v>
+        <v>47.20471946369999</v>
       </c>
       <c r="Q56">
-        <v>87.50507156435998</v>
+        <v>87.10471946369999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09292964461702953</v>
+        <v>0.0938381164405454</v>
       </c>
       <c r="T56">
-        <v>1.088444448430243</v>
+        <v>1.10942532195255</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.202000184054685</v>
+        <v>3.143781998890054</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06868955539824542</v>
+        <v>0.06865020587265729</v>
       </c>
       <c r="C57">
-        <v>302.9254479818733</v>
+        <v>295.2812717475302</v>
       </c>
       <c r="D57">
-        <v>727.2804479818734</v>
+        <v>727.9572717475303</v>
       </c>
       <c r="E57">
-        <v>-12.34499999999997</v>
+        <v>-4.023999999999944</v>
       </c>
       <c r="F57">
-        <v>457.655</v>
+        <v>465.9760000000001</v>
       </c>
       <c r="G57">
         <v>33.3</v>
@@ -5961,28 +5961,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M57">
-        <v>29.3356855</v>
+        <v>29.86906160000001</v>
       </c>
       <c r="N57">
-        <v>62.88931449999999</v>
+        <v>62.35593839999999</v>
       </c>
       <c r="O57">
-        <v>15.6845950363</v>
+        <v>15.55157103696</v>
       </c>
       <c r="P57">
-        <v>47.20471946369999</v>
+        <v>46.80436736303999</v>
       </c>
       <c r="Q57">
-        <v>87.10471946369999</v>
+        <v>86.70436736303998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.0938381164405454</v>
+        <v>0.09478788243785746</v>
       </c>
       <c r="T57">
-        <v>1.10942532195255</v>
+        <v>1.131359871544052</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.143781998890054</v>
+        <v>3.08764303462416</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06865020587265729</v>
+        <v>0.06861085634706912</v>
       </c>
       <c r="C58">
-        <v>295.2812717475302</v>
+        <v>287.6383564218716</v>
       </c>
       <c r="D58">
-        <v>727.9572717475303</v>
+        <v>728.6353564218717</v>
       </c>
       <c r="E58">
-        <v>-4.023999999999944</v>
+        <v>4.297000000000082</v>
       </c>
       <c r="F58">
-        <v>465.9760000000001</v>
+        <v>474.2970000000001</v>
       </c>
       <c r="G58">
         <v>33.3</v>
@@ -6043,28 +6043,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M58">
-        <v>29.86906160000001</v>
+        <v>30.40243770000001</v>
       </c>
       <c r="N58">
-        <v>62.35593839999999</v>
+        <v>61.82256229999999</v>
       </c>
       <c r="O58">
-        <v>15.55157103696</v>
+        <v>15.41854703762</v>
       </c>
       <c r="P58">
-        <v>46.80436736303999</v>
+        <v>46.40401526237999</v>
       </c>
       <c r="Q58">
-        <v>86.70436736303998</v>
+        <v>86.30401526237998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09478788243785746</v>
+        <v>0.09578182359783519</v>
       </c>
       <c r="T58">
-        <v>1.131359871544052</v>
+        <v>1.154314632744462</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.08764303462416</v>
+        <v>3.033473858578122</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06861085634706912</v>
+        <v>0.07196722122148097</v>
       </c>
       <c r="C59">
-        <v>287.6383564218716</v>
+        <v>225.6865408685347</v>
       </c>
       <c r="D59">
-        <v>728.6353564218717</v>
+        <v>675.0045408685348</v>
       </c>
       <c r="E59">
-        <v>4.297000000000082</v>
+        <v>12.61800000000005</v>
       </c>
       <c r="F59">
-        <v>474.2970000000001</v>
+        <v>482.6180000000001</v>
       </c>
       <c r="G59">
         <v>33.3</v>
@@ -6125,45 +6125,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M59">
-        <v>30.40243770000001</v>
+        <v>34.7002342</v>
       </c>
       <c r="N59">
-        <v>61.82256229999999</v>
+        <v>57.52476579999999</v>
       </c>
       <c r="O59">
-        <v>15.41854703762</v>
+        <v>14.34667659052</v>
       </c>
       <c r="P59">
-        <v>46.40401526237999</v>
+        <v>43.17808920947999</v>
       </c>
       <c r="Q59">
-        <v>86.30401526237998</v>
+        <v>83.07808920948</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09578182359783519</v>
+        <v>0.09682309528924044</v>
       </c>
       <c r="T59">
-        <v>1.154314632744462</v>
+        <v>1.178362477811557</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.2494</v>
       </c>
       <c r="W59">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.033473858578122</v>
+        <v>2.657763041841371</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07196722122148098</v>
+        <v>0.07198641849589282</v>
       </c>
       <c r="C60">
-        <v>225.6865408685346</v>
+        <v>217.0814884681632</v>
       </c>
       <c r="D60">
-        <v>675.0045408685346</v>
+        <v>674.7204884681632</v>
       </c>
       <c r="E60">
-        <v>12.61799999999999</v>
+        <v>20.93899999999996</v>
       </c>
       <c r="F60">
-        <v>482.618</v>
+        <v>490.939</v>
       </c>
       <c r="G60">
         <v>33.3</v>
@@ -6207,28 +6207,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M60">
-        <v>34.7002342</v>
+        <v>35.2985141</v>
       </c>
       <c r="N60">
-        <v>57.52476579999999</v>
+        <v>56.9264859</v>
       </c>
       <c r="O60">
-        <v>14.34667659052</v>
+        <v>14.19746558346</v>
       </c>
       <c r="P60">
-        <v>43.17808920947999</v>
+        <v>42.72902031653999</v>
       </c>
       <c r="Q60">
-        <v>83.07808920948</v>
+        <v>82.62902031653999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09682309528924044</v>
+        <v>0.09791516072168982</v>
       </c>
       <c r="T60">
-        <v>1.178362477811557</v>
+        <v>1.203583388491682</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.657763041841371</v>
+        <v>2.612716210623721</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07198641849589282</v>
+        <v>0.07200561577030468</v>
       </c>
       <c r="C61">
-        <v>217.0814884681632</v>
+        <v>208.4766750345592</v>
       </c>
       <c r="D61">
-        <v>674.7204884681632</v>
+        <v>674.4366750345592</v>
       </c>
       <c r="E61">
-        <v>20.93899999999996</v>
+        <v>29.25999999999999</v>
       </c>
       <c r="F61">
-        <v>490.939</v>
+        <v>499.26</v>
       </c>
       <c r="G61">
         <v>33.3</v>
@@ -6289,28 +6289,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M61">
-        <v>35.2985141</v>
+        <v>35.896794</v>
       </c>
       <c r="N61">
-        <v>56.9264859</v>
+        <v>56.32820599999999</v>
       </c>
       <c r="O61">
-        <v>14.19746558346</v>
+        <v>14.0482545764</v>
       </c>
       <c r="P61">
-        <v>42.72902031653999</v>
+        <v>42.2799514236</v>
       </c>
       <c r="Q61">
-        <v>82.62902031653999</v>
+        <v>82.17995142359999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09791516072168982</v>
+        <v>0.09906182942576169</v>
       </c>
       <c r="T61">
-        <v>1.203583388491682</v>
+        <v>1.230065344705813</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.612716210623721</v>
+        <v>2.569170940446659</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07200561577030468</v>
+        <v>0.07202481304471653</v>
       </c>
       <c r="C62">
-        <v>208.4766750345592</v>
+        <v>199.8721002662936</v>
       </c>
       <c r="D62">
-        <v>674.4366750345592</v>
+        <v>674.1531002662937</v>
       </c>
       <c r="E62">
-        <v>29.25999999999999</v>
+        <v>37.58100000000002</v>
       </c>
       <c r="F62">
-        <v>499.26</v>
+        <v>507.581</v>
       </c>
       <c r="G62">
         <v>33.3</v>
@@ -6371,28 +6371,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M62">
-        <v>35.896794</v>
+        <v>36.4950739</v>
       </c>
       <c r="N62">
-        <v>56.32820599999999</v>
+        <v>55.72992609999999</v>
       </c>
       <c r="O62">
-        <v>14.0482545764</v>
+        <v>13.89904356934</v>
       </c>
       <c r="P62">
-        <v>42.2799514236</v>
+        <v>41.83088253065999</v>
       </c>
       <c r="Q62">
-        <v>82.17995142359999</v>
+        <v>81.73088253065998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09906182942576169</v>
+        <v>0.1002673016531193</v>
       </c>
       <c r="T62">
-        <v>1.230065344705813</v>
+        <v>1.257905349956566</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.569170940446659</v>
+        <v>2.527053384045894</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07202481304471653</v>
+        <v>0.07385896111912837</v>
       </c>
       <c r="C63">
-        <v>199.8721002662936</v>
+        <v>165.5150745659346</v>
       </c>
       <c r="D63">
-        <v>674.1531002662937</v>
+        <v>648.1170745659347</v>
       </c>
       <c r="E63">
-        <v>37.58100000000002</v>
+        <v>45.90200000000004</v>
       </c>
       <c r="F63">
-        <v>507.581</v>
+        <v>515.902</v>
       </c>
       <c r="G63">
         <v>33.3</v>
@@ -6453,45 +6453,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M63">
-        <v>36.4950739</v>
+        <v>39.10537160000001</v>
       </c>
       <c r="N63">
-        <v>55.72992609999999</v>
+        <v>53.11962839999999</v>
       </c>
       <c r="O63">
-        <v>13.89904356934</v>
+        <v>13.24803532296</v>
       </c>
       <c r="P63">
-        <v>41.83088253065999</v>
+        <v>39.87159307703999</v>
       </c>
       <c r="Q63">
-        <v>81.73088253065998</v>
+        <v>79.77159307704</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1002673016531193</v>
+        <v>0.1015362197871799</v>
       </c>
       <c r="T63">
-        <v>1.257905349956566</v>
+        <v>1.287210618641569</v>
       </c>
       <c r="U63">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.2494</v>
       </c>
       <c r="W63">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.527053384045894</v>
+        <v>2.358371656542448</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07385896111912837</v>
+        <v>0.07390743179354023</v>
       </c>
       <c r="C64">
-        <v>165.5150745659346</v>
+        <v>156.5332726910948</v>
       </c>
       <c r="D64">
-        <v>648.1170745659347</v>
+        <v>647.4562726910949</v>
       </c>
       <c r="E64">
-        <v>45.90200000000004</v>
+        <v>54.22300000000007</v>
       </c>
       <c r="F64">
-        <v>515.902</v>
+        <v>524.2230000000001</v>
       </c>
       <c r="G64">
         <v>33.3</v>
@@ -6535,28 +6535,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M64">
-        <v>39.10537160000001</v>
+        <v>39.73610340000001</v>
       </c>
       <c r="N64">
-        <v>53.11962839999999</v>
+        <v>52.48889659999998</v>
       </c>
       <c r="O64">
-        <v>13.24803532296</v>
+        <v>13.09073081204</v>
       </c>
       <c r="P64">
-        <v>39.87159307703999</v>
+        <v>39.39816578795998</v>
       </c>
       <c r="Q64">
-        <v>79.77159307704</v>
+        <v>79.29816578795999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1015362197871799</v>
+        <v>0.1028737280906493</v>
       </c>
       <c r="T64">
-        <v>1.287210618641569</v>
+        <v>1.31809995590414</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.358371656542448</v>
+        <v>2.320937185803678</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07390743179354023</v>
+        <v>0.07395590246795208</v>
       </c>
       <c r="C65">
-        <v>156.5332726910948</v>
+        <v>147.5528169136905</v>
       </c>
       <c r="D65">
-        <v>647.4562726910949</v>
+        <v>646.7968169136906</v>
       </c>
       <c r="E65">
-        <v>54.22300000000007</v>
+        <v>62.54399999999998</v>
       </c>
       <c r="F65">
-        <v>524.2230000000001</v>
+        <v>532.544</v>
       </c>
       <c r="G65">
         <v>33.3</v>
@@ -6617,28 +6617,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M65">
-        <v>39.73610340000001</v>
+        <v>40.3668352</v>
       </c>
       <c r="N65">
-        <v>52.48889659999998</v>
+        <v>51.85816479999999</v>
       </c>
       <c r="O65">
-        <v>13.09073081204</v>
+        <v>12.93342630112</v>
       </c>
       <c r="P65">
-        <v>39.39816578795998</v>
+        <v>38.92473849887999</v>
       </c>
       <c r="Q65">
-        <v>79.29816578795999</v>
+        <v>78.82473849887998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1028737280906493</v>
+        <v>0.104285542410978</v>
       </c>
       <c r="T65">
-        <v>1.31809995590414</v>
+        <v>1.350705367459076</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.320937185803678</v>
+        <v>2.284672542275496</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07395590246795208</v>
+        <v>0.07400437314236392</v>
       </c>
       <c r="C66">
-        <v>147.5528169136905</v>
+        <v>138.5737031247716</v>
       </c>
       <c r="D66">
-        <v>646.7968169136906</v>
+        <v>646.1387031247716</v>
       </c>
       <c r="E66">
-        <v>62.54399999999998</v>
+        <v>70.86500000000001</v>
       </c>
       <c r="F66">
-        <v>532.544</v>
+        <v>540.865</v>
       </c>
       <c r="G66">
         <v>33.3</v>
@@ -6699,28 +6699,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M66">
-        <v>40.3668352</v>
+        <v>40.997567</v>
       </c>
       <c r="N66">
-        <v>51.85816479999999</v>
+        <v>51.22743299999999</v>
       </c>
       <c r="O66">
-        <v>12.93342630112</v>
+        <v>12.7761217902</v>
       </c>
       <c r="P66">
-        <v>38.92473849887999</v>
+        <v>38.4513112098</v>
       </c>
       <c r="Q66">
-        <v>78.82473849887998</v>
+        <v>78.3513112098</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.104285542410978</v>
+        <v>0.1057780318353255</v>
       </c>
       <c r="T66">
-        <v>1.350705367459076</v>
+        <v>1.38517394538858</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.284672542275496</v>
+        <v>2.249523733932796</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07400437314236392</v>
+        <v>0.07405284381677577</v>
       </c>
       <c r="C67">
-        <v>138.5737031247716</v>
+        <v>129.595927232094</v>
       </c>
       <c r="D67">
-        <v>646.1387031247716</v>
+        <v>645.4819272320941</v>
       </c>
       <c r="E67">
-        <v>70.86500000000001</v>
+        <v>79.18600000000004</v>
       </c>
       <c r="F67">
-        <v>540.865</v>
+        <v>549.186</v>
       </c>
       <c r="G67">
         <v>33.3</v>
@@ -6781,28 +6781,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M67">
-        <v>40.997567</v>
+        <v>41.6282988</v>
       </c>
       <c r="N67">
-        <v>51.22743299999999</v>
+        <v>50.59670119999999</v>
       </c>
       <c r="O67">
-        <v>12.7761217902</v>
+        <v>12.61881727928</v>
       </c>
       <c r="P67">
-        <v>38.4513112098</v>
+        <v>37.97788392071999</v>
       </c>
       <c r="Q67">
-        <v>78.3513112098</v>
+        <v>77.87788392072</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1057780318353255</v>
+        <v>0.1073583147552229</v>
       </c>
       <c r="T67">
-        <v>1.38517394538858</v>
+        <v>1.421670086725701</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.249523733932796</v>
+        <v>2.21544004099442</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07405284381677577</v>
+        <v>0.07410131449118762</v>
       </c>
       <c r="C68">
-        <v>129.595927232094</v>
+        <v>120.6194851600358</v>
       </c>
       <c r="D68">
-        <v>645.4819272320941</v>
+        <v>644.8264851600359</v>
       </c>
       <c r="E68">
-        <v>79.18600000000004</v>
+        <v>87.50700000000006</v>
       </c>
       <c r="F68">
-        <v>549.186</v>
+        <v>557.5070000000001</v>
       </c>
       <c r="G68">
         <v>33.3</v>
@@ -6863,28 +6863,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M68">
-        <v>41.6282988</v>
+        <v>42.25903060000001</v>
       </c>
       <c r="N68">
-        <v>50.59670119999999</v>
+        <v>49.96596939999998</v>
       </c>
       <c r="O68">
-        <v>12.61881727928</v>
+        <v>12.46151276836</v>
       </c>
       <c r="P68">
-        <v>37.97788392071999</v>
+        <v>37.50445663163999</v>
       </c>
       <c r="Q68">
-        <v>77.87788392072</v>
+        <v>77.40445663163999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1073583147552229</v>
+        <v>0.1090343723975383</v>
       </c>
       <c r="T68">
-        <v>1.421670086725701</v>
+        <v>1.460378115416588</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.21544004099442</v>
+        <v>2.182373771725847</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07410131449118762</v>
+        <v>0.07414978516559947</v>
       </c>
       <c r="C69">
-        <v>120.6194851600358</v>
+        <v>111.6443728495118</v>
       </c>
       <c r="D69">
-        <v>644.8264851600359</v>
+        <v>644.1723728495119</v>
       </c>
       <c r="E69">
-        <v>87.50700000000006</v>
+        <v>95.82800000000009</v>
       </c>
       <c r="F69">
-        <v>557.5070000000001</v>
+        <v>565.8280000000001</v>
       </c>
       <c r="G69">
         <v>33.3</v>
@@ -6945,28 +6945,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M69">
-        <v>42.25903060000001</v>
+        <v>42.88976240000001</v>
       </c>
       <c r="N69">
-        <v>49.96596939999998</v>
+        <v>49.33523759999999</v>
       </c>
       <c r="O69">
-        <v>12.46151276836</v>
+        <v>12.30420825744</v>
       </c>
       <c r="P69">
-        <v>37.50445663163999</v>
+        <v>37.03102934255999</v>
       </c>
       <c r="Q69">
-        <v>77.40445663163999</v>
+        <v>76.93102934255998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1090343723975383</v>
+        <v>0.1108151836424984</v>
       </c>
       <c r="T69">
-        <v>1.460378115416588</v>
+        <v>1.501505395900655</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.182373771725847</v>
+        <v>2.150280039788702</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07414978516559947</v>
+        <v>0.07419825584001133</v>
       </c>
       <c r="C70">
-        <v>111.6443728495118</v>
+        <v>102.6705862578908</v>
       </c>
       <c r="D70">
-        <v>644.1723728495119</v>
+        <v>643.519586257891</v>
       </c>
       <c r="E70">
-        <v>95.82800000000009</v>
+        <v>104.1490000000001</v>
       </c>
       <c r="F70">
-        <v>565.8280000000001</v>
+        <v>574.1490000000001</v>
       </c>
       <c r="G70">
         <v>33.3</v>
@@ -7027,28 +7027,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M70">
-        <v>42.88976240000001</v>
+        <v>43.52049420000001</v>
       </c>
       <c r="N70">
-        <v>49.33523759999999</v>
+        <v>48.70450579999999</v>
       </c>
       <c r="O70">
-        <v>12.30420825744</v>
+        <v>12.14690374652</v>
       </c>
       <c r="P70">
-        <v>37.03102934255999</v>
+        <v>36.55760205347999</v>
       </c>
       <c r="Q70">
-        <v>76.93102934255998</v>
+        <v>76.45760205347999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1108151836424984</v>
+        <v>0.1127108859355204</v>
       </c>
       <c r="T70">
-        <v>1.501505395900655</v>
+        <v>1.545286049319178</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.150280039788702</v>
+        <v>2.119116560951185</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07419825584001133</v>
+        <v>0.07424672651442317</v>
       </c>
       <c r="C71">
-        <v>102.6705862578908</v>
+        <v>93.69812135891175</v>
       </c>
       <c r="D71">
-        <v>643.519586257891</v>
+        <v>642.8681213589118</v>
       </c>
       <c r="E71">
-        <v>104.1490000000001</v>
+        <v>112.47</v>
       </c>
       <c r="F71">
-        <v>574.1490000000001</v>
+        <v>582.47</v>
       </c>
       <c r="G71">
         <v>33.3</v>
@@ -7109,28 +7109,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M71">
-        <v>43.52049420000001</v>
+        <v>44.15122600000001</v>
       </c>
       <c r="N71">
-        <v>48.70450579999999</v>
+        <v>48.07377399999999</v>
       </c>
       <c r="O71">
-        <v>12.14690374652</v>
+        <v>11.9895992356</v>
       </c>
       <c r="P71">
-        <v>36.55760205347999</v>
+        <v>36.08417476439999</v>
       </c>
       <c r="Q71">
-        <v>76.45760205347999</v>
+        <v>75.9841747644</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1127108859355204</v>
+        <v>0.1147329683814106</v>
       </c>
       <c r="T71">
-        <v>1.545286049319178</v>
+        <v>1.591985412965602</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.119116560951185</v>
+        <v>2.08884346722331</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07424672651442317</v>
+        <v>0.07429519718883502</v>
       </c>
       <c r="C72">
-        <v>93.69812135891175</v>
+        <v>84.7269741426004</v>
       </c>
       <c r="D72">
-        <v>642.8681213589118</v>
+        <v>642.2179741426005</v>
       </c>
       <c r="E72">
-        <v>112.47</v>
+        <v>120.7910000000001</v>
       </c>
       <c r="F72">
-        <v>582.47</v>
+        <v>590.7910000000001</v>
       </c>
       <c r="G72">
         <v>33.3</v>
@@ -7191,28 +7191,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M72">
-        <v>44.15122600000001</v>
+        <v>44.78195780000001</v>
       </c>
       <c r="N72">
-        <v>48.07377399999999</v>
+        <v>47.44304219999999</v>
       </c>
       <c r="O72">
-        <v>11.9895992356</v>
+        <v>11.83229472468</v>
       </c>
       <c r="P72">
-        <v>36.08417476439999</v>
+        <v>35.61074747531999</v>
       </c>
       <c r="Q72">
-        <v>75.9841747644</v>
+        <v>75.51074747531999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1147329683814106</v>
+        <v>0.1168945047890863</v>
       </c>
       <c r="T72">
-        <v>1.591985412965602</v>
+        <v>1.641905422380746</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.08884346722331</v>
+        <v>2.059423136699039</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07429519718883502</v>
+        <v>0.07434366786324687</v>
       </c>
       <c r="C73">
-        <v>84.72697414260051</v>
+        <v>75.75714061518818</v>
       </c>
       <c r="D73">
-        <v>642.2179741426005</v>
+        <v>641.5691406151882</v>
       </c>
       <c r="E73">
-        <v>120.7909999999999</v>
+        <v>129.112</v>
       </c>
       <c r="F73">
-        <v>590.7909999999999</v>
+        <v>599.112</v>
       </c>
       <c r="G73">
         <v>33.3</v>
@@ -7273,28 +7273,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M73">
-        <v>44.7819578</v>
+        <v>45.4126896</v>
       </c>
       <c r="N73">
-        <v>47.44304219999999</v>
+        <v>46.81231039999999</v>
       </c>
       <c r="O73">
-        <v>11.83229472468</v>
+        <v>11.67499021376</v>
       </c>
       <c r="P73">
-        <v>35.61074747532</v>
+        <v>35.13732018624</v>
       </c>
       <c r="Q73">
-        <v>75.51074747531999</v>
+        <v>75.03732018624</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1168945047890863</v>
+        <v>0.1192104366544531</v>
       </c>
       <c r="T73">
-        <v>1.641905422380745</v>
+        <v>1.695391146754113</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.059423136699039</v>
+        <v>2.030820037578219</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07434366786324687</v>
+        <v>0.07439213853765872</v>
       </c>
       <c r="C74">
-        <v>75.75714061518818</v>
+        <v>66.78861679902934</v>
       </c>
       <c r="D74">
-        <v>641.5691406151882</v>
+        <v>640.9216167990294</v>
       </c>
       <c r="E74">
-        <v>129.112</v>
+        <v>137.433</v>
       </c>
       <c r="F74">
-        <v>599.112</v>
+        <v>607.433</v>
       </c>
       <c r="G74">
         <v>33.3</v>
@@ -7355,28 +7355,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M74">
-        <v>45.4126896</v>
+        <v>46.0434214</v>
       </c>
       <c r="N74">
-        <v>46.81231039999999</v>
+        <v>46.18157859999999</v>
       </c>
       <c r="O74">
-        <v>11.67499021376</v>
+        <v>11.51768570284</v>
       </c>
       <c r="P74">
-        <v>35.13732018624</v>
+        <v>34.66389289716</v>
       </c>
       <c r="Q74">
-        <v>75.03732018624</v>
+        <v>74.56389289716</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1192104366544531</v>
+        <v>0.1216979190283656</v>
       </c>
       <c r="T74">
-        <v>1.695391146754113</v>
+        <v>1.752838776636619</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.030820037578219</v>
+        <v>2.003000585008654</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07439213853765872</v>
+        <v>0.08232791401207055</v>
       </c>
       <c r="C75">
-        <v>66.78861679902934</v>
+        <v>-32.42133082550379</v>
       </c>
       <c r="D75">
-        <v>640.9216167990294</v>
+        <v>550.0326691744963</v>
       </c>
       <c r="E75">
-        <v>137.433</v>
+        <v>145.754</v>
       </c>
       <c r="F75">
-        <v>607.433</v>
+        <v>615.754</v>
       </c>
       <c r="G75">
         <v>33.3</v>
@@ -7437,45 +7437,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M75">
-        <v>46.0434214</v>
+        <v>55.41786</v>
       </c>
       <c r="N75">
-        <v>46.18157859999999</v>
+        <v>36.80714</v>
       </c>
       <c r="O75">
-        <v>11.51768570284</v>
+        <v>9.179700715999999</v>
       </c>
       <c r="P75">
-        <v>34.66389289716</v>
+        <v>27.627439284</v>
       </c>
       <c r="Q75">
-        <v>74.56389289716</v>
+        <v>67.527439284</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1216979190283656</v>
+        <v>0.1243767462002714</v>
       </c>
       <c r="T75">
-        <v>1.752838776636619</v>
+        <v>1.814705454971626</v>
       </c>
       <c r="U75">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
         <v>0.2494</v>
       </c>
       <c r="W75">
-        <v>0.05689548</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.003000585008654</v>
+        <v>1.664174690253287</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08232791401207055</v>
+        <v>0.0824829698864824</v>
       </c>
       <c r="C76">
-        <v>-32.42133082550379</v>
+        <v>-42.26214963259622</v>
       </c>
       <c r="D76">
-        <v>550.0326691744963</v>
+        <v>548.5128503674039</v>
       </c>
       <c r="E76">
-        <v>145.754</v>
+        <v>154.075</v>
       </c>
       <c r="F76">
-        <v>615.754</v>
+        <v>624.075</v>
       </c>
       <c r="G76">
         <v>33.3</v>
@@ -7519,28 +7519,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M76">
-        <v>55.41786</v>
+        <v>56.16675</v>
       </c>
       <c r="N76">
-        <v>36.80714</v>
+        <v>36.05824999999999</v>
       </c>
       <c r="O76">
-        <v>9.179700715999999</v>
+        <v>8.992927549999999</v>
       </c>
       <c r="P76">
-        <v>27.627439284</v>
+        <v>27.06532245</v>
       </c>
       <c r="Q76">
-        <v>67.527439284</v>
+        <v>66.96532245</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1243767462002714</v>
+        <v>0.1272698795459297</v>
       </c>
       <c r="T76">
-        <v>1.814705454971626</v>
+        <v>1.881521467573433</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.664174690253287</v>
+        <v>1.641985694383242</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0824829698864824</v>
+        <v>0.08263802576089427</v>
       </c>
       <c r="C77">
-        <v>-42.26214963259622</v>
+        <v>-52.09459263047108</v>
       </c>
       <c r="D77">
-        <v>548.5128503674039</v>
+        <v>547.001407369529</v>
       </c>
       <c r="E77">
-        <v>154.075</v>
+        <v>162.3960000000001</v>
       </c>
       <c r="F77">
-        <v>624.075</v>
+        <v>632.3960000000001</v>
       </c>
       <c r="G77">
         <v>33.3</v>
@@ -7601,28 +7601,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M77">
-        <v>56.16675</v>
+        <v>56.91564</v>
       </c>
       <c r="N77">
-        <v>36.05824999999999</v>
+        <v>35.30935999999999</v>
       </c>
       <c r="O77">
-        <v>8.992927549999999</v>
+        <v>8.806154383999997</v>
       </c>
       <c r="P77">
-        <v>27.06532245</v>
+        <v>26.503205616</v>
       </c>
       <c r="Q77">
-        <v>66.96532245</v>
+        <v>66.40320561599999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1272698795459297</v>
+        <v>0.1304041073370595</v>
       </c>
       <c r="T77">
-        <v>1.881521467573433</v>
+        <v>1.953905481225391</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.641985694383242</v>
+        <v>1.620380619457147</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08263802576089427</v>
+        <v>0.0827930816353061</v>
       </c>
       <c r="C78">
-        <v>-52.09459263047108</v>
+        <v>-61.91872886821398</v>
       </c>
       <c r="D78">
-        <v>547.001407369529</v>
+        <v>545.4982711317861</v>
       </c>
       <c r="E78">
-        <v>162.3960000000001</v>
+        <v>170.717</v>
       </c>
       <c r="F78">
-        <v>632.3960000000001</v>
+        <v>640.717</v>
       </c>
       <c r="G78">
         <v>33.3</v>
@@ -7683,28 +7683,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M78">
-        <v>56.91564</v>
+        <v>57.66453</v>
       </c>
       <c r="N78">
-        <v>35.30935999999999</v>
+        <v>34.56047</v>
       </c>
       <c r="O78">
-        <v>8.806154383999997</v>
+        <v>8.619381217999999</v>
       </c>
       <c r="P78">
-        <v>26.503205616</v>
+        <v>25.94108878199999</v>
       </c>
       <c r="Q78">
-        <v>66.40320561599999</v>
+        <v>65.84108878199999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1304041073370595</v>
+        <v>0.133810876675244</v>
       </c>
       <c r="T78">
-        <v>1.953905481225391</v>
+        <v>2.032583756934041</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.620380619457147</v>
+        <v>1.599336715308353</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0827930816353061</v>
+        <v>0.08294813750971795</v>
       </c>
       <c r="C79">
-        <v>-61.91872886821398</v>
+        <v>-71.73462663801513</v>
       </c>
       <c r="D79">
-        <v>545.4982711317861</v>
+        <v>544.0033733619849</v>
       </c>
       <c r="E79">
-        <v>170.717</v>
+        <v>179.038</v>
       </c>
       <c r="F79">
-        <v>640.717</v>
+        <v>649.038</v>
       </c>
       <c r="G79">
         <v>33.3</v>
@@ -7765,28 +7765,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M79">
-        <v>57.66453</v>
+        <v>58.41342</v>
       </c>
       <c r="N79">
-        <v>34.56047</v>
+        <v>33.81157999999999</v>
       </c>
       <c r="O79">
-        <v>8.619381217999999</v>
+        <v>8.432608051999999</v>
       </c>
       <c r="P79">
-        <v>25.94108878199999</v>
+        <v>25.37897194799999</v>
       </c>
       <c r="Q79">
-        <v>65.84108878199999</v>
+        <v>65.27897194799999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.133810876675244</v>
+        <v>0.1375273523168998</v>
       </c>
       <c r="T79">
-        <v>2.032583756934041</v>
+        <v>2.118414603161659</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.599336715308353</v>
+        <v>1.578832398445426</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08294813750971795</v>
+        <v>0.0831031933841298</v>
       </c>
       <c r="C80">
-        <v>-71.73462663801513</v>
+        <v>-81.54235348551163</v>
       </c>
       <c r="D80">
-        <v>544.0033733619849</v>
+        <v>542.5166465144885</v>
       </c>
       <c r="E80">
-        <v>179.038</v>
+        <v>187.359</v>
       </c>
       <c r="F80">
-        <v>649.038</v>
+        <v>657.359</v>
       </c>
       <c r="G80">
         <v>33.3</v>
@@ -7847,28 +7847,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M80">
-        <v>58.41342</v>
+        <v>59.16231</v>
       </c>
       <c r="N80">
-        <v>33.81157999999999</v>
+        <v>33.06269</v>
       </c>
       <c r="O80">
-        <v>8.432608051999999</v>
+        <v>8.245834885999999</v>
       </c>
       <c r="P80">
-        <v>25.37897194799999</v>
+        <v>24.816855114</v>
       </c>
       <c r="Q80">
-        <v>65.27897194799999</v>
+        <v>64.716855114</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1375273523168998</v>
+        <v>0.1415977780196658</v>
       </c>
       <c r="T80">
-        <v>2.118414603161659</v>
+        <v>2.212419815696669</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.578832398445426</v>
+        <v>1.558847178211939</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0831031933841298</v>
+        <v>0.08325824925854165</v>
       </c>
       <c r="C81">
-        <v>-81.54235348551163</v>
+        <v>-91.34197621996123</v>
       </c>
       <c r="D81">
-        <v>542.5166465144885</v>
+        <v>541.0380237800389</v>
       </c>
       <c r="E81">
-        <v>187.359</v>
+        <v>195.6800000000001</v>
       </c>
       <c r="F81">
-        <v>657.359</v>
+        <v>665.6800000000001</v>
       </c>
       <c r="G81">
         <v>33.3</v>
@@ -7929,28 +7929,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M81">
-        <v>59.16231</v>
+        <v>59.9112</v>
       </c>
       <c r="N81">
-        <v>33.06269</v>
+        <v>32.31379999999999</v>
       </c>
       <c r="O81">
-        <v>8.245834885999999</v>
+        <v>8.059061719999999</v>
       </c>
       <c r="P81">
-        <v>24.816855114</v>
+        <v>24.25473827999999</v>
       </c>
       <c r="Q81">
-        <v>64.716855114</v>
+        <v>64.15473827999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1415977780196658</v>
+        <v>0.1460752462927083</v>
       </c>
       <c r="T81">
-        <v>2.212419815696669</v>
+        <v>2.315825549485181</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.558847178211939</v>
+        <v>1.53936158848429</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08325824925854165</v>
+        <v>0.0834133051329535</v>
       </c>
       <c r="C82">
-        <v>-91.34197621996123</v>
+        <v>-101.1335609242497</v>
       </c>
       <c r="D82">
-        <v>541.0380237800389</v>
+        <v>539.5674390757505</v>
       </c>
       <c r="E82">
-        <v>195.6800000000001</v>
+        <v>204.0010000000001</v>
       </c>
       <c r="F82">
-        <v>665.6800000000001</v>
+        <v>674.0010000000001</v>
       </c>
       <c r="G82">
         <v>33.3</v>
@@ -8011,28 +8011,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M82">
-        <v>59.9112</v>
+        <v>60.66009</v>
       </c>
       <c r="N82">
-        <v>32.31379999999999</v>
+        <v>31.56490999999999</v>
       </c>
       <c r="O82">
-        <v>8.059061719999999</v>
+        <v>7.872288553999998</v>
       </c>
       <c r="P82">
-        <v>24.25473827999999</v>
+        <v>23.69262144599999</v>
       </c>
       <c r="Q82">
-        <v>64.15473827999999</v>
+        <v>63.592621446</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1460752462927083</v>
+        <v>0.1510240270155448</v>
       </c>
       <c r="T82">
-        <v>2.315825549485181</v>
+        <v>2.430116097356693</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.53936158848429</v>
+        <v>1.520357124428928</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.0834133051329535</v>
+        <v>0.08356836100736537</v>
       </c>
       <c r="C83">
-        <v>-101.1335609242497</v>
+        <v>-110.9171729647366</v>
       </c>
       <c r="D83">
-        <v>539.5674390757505</v>
+        <v>538.1048270352636</v>
       </c>
       <c r="E83">
-        <v>204.0010000000001</v>
+        <v>212.3220000000001</v>
       </c>
       <c r="F83">
-        <v>674.0010000000001</v>
+        <v>682.3220000000001</v>
       </c>
       <c r="G83">
         <v>33.3</v>
@@ -8093,28 +8093,28 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M83">
-        <v>60.66009</v>
+        <v>61.40898000000001</v>
       </c>
       <c r="N83">
-        <v>31.56490999999999</v>
+        <v>30.81601999999999</v>
       </c>
       <c r="O83">
-        <v>7.872288553999998</v>
+        <v>7.685515387999997</v>
       </c>
       <c r="P83">
-        <v>23.69262144599999</v>
+        <v>23.13050461199999</v>
       </c>
       <c r="Q83">
-        <v>63.592621446</v>
+        <v>63.03050461199999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1510240270155448</v>
+        <v>0.156522672263141</v>
       </c>
       <c r="T83">
-        <v>2.430116097356693</v>
+        <v>2.557105594991707</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.520357124428928</v>
+        <v>1.501816183887112</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08356836100736537</v>
+        <v>0.1223242181886279</v>
       </c>
       <c r="C84">
-        <v>-110.9171729647366</v>
+        <v>-336.5720905153385</v>
       </c>
       <c r="D84">
-        <v>538.1048270352636</v>
+        <v>320.7709094846616</v>
       </c>
       <c r="E84">
-        <v>212.3220000000001</v>
+        <v>220.643</v>
       </c>
       <c r="F84">
-        <v>682.3220000000001</v>
+        <v>690.643</v>
       </c>
       <c r="G84">
         <v>33.3</v>
@@ -8175,45 +8175,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M84">
-        <v>61.40898000000001</v>
+        <v>101.3863924</v>
       </c>
       <c r="N84">
-        <v>30.81601999999999</v>
+        <v>-9.161392400000025</v>
       </c>
       <c r="O84">
-        <v>7.685515387999997</v>
+        <v>-2.284851264560007</v>
       </c>
       <c r="P84">
-        <v>23.13050461199999</v>
+        <v>-6.876541135440019</v>
       </c>
       <c r="Q84">
-        <v>63.03050461199999</v>
+        <v>33.02345886455998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.156522672263141</v>
+        <v>0.1654248609454272</v>
       </c>
       <c r="T84">
-        <v>2.557105594991707</v>
+        <v>2.762698867099935</v>
       </c>
       <c r="U84">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2494</v>
+        <v>0.2268639257747176</v>
       </c>
       <c r="W84">
-        <v>0.06755399999999999</v>
+        <v>0.1134963756962715</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.501816183887112</v>
+        <v>0.9096388363060048</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1223242181886279</v>
+        <v>0.1233342181886279</v>
       </c>
       <c r="C85">
-        <v>-336.5720905153385</v>
+        <v>-348.2342124531334</v>
       </c>
       <c r="D85">
-        <v>320.7709094846616</v>
+        <v>317.4297875468667</v>
       </c>
       <c r="E85">
-        <v>220.643</v>
+        <v>228.9640000000001</v>
       </c>
       <c r="F85">
-        <v>690.643</v>
+        <v>698.9640000000001</v>
       </c>
       <c r="G85">
         <v>33.3</v>
@@ -8257,37 +8257,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M85">
-        <v>101.3863924</v>
+        <v>102.6079152</v>
       </c>
       <c r="N85">
-        <v>-9.161392400000025</v>
+        <v>-10.38291520000003</v>
       </c>
       <c r="O85">
-        <v>-2.284851264560007</v>
+        <v>-2.589499050880007</v>
       </c>
       <c r="P85">
-        <v>-6.876541135440019</v>
+        <v>-7.793416149120021</v>
       </c>
       <c r="Q85">
-        <v>33.02345886455998</v>
+        <v>32.10658385087998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1654248609454272</v>
+        <v>0.1729014147545165</v>
       </c>
       <c r="T85">
-        <v>2.762698867099935</v>
+        <v>2.935367546293682</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2268639257747176</v>
+        <v>0.22416316475359</v>
       </c>
       <c r="W85">
-        <v>0.1134963756962715</v>
+        <v>0.113892847414173</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9096388363060048</v>
+        <v>0.8988098025404572</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1233342181886279</v>
+        <v>0.1243442181886279</v>
       </c>
       <c r="C86">
-        <v>-348.2342124531332</v>
+        <v>-359.8274502106388</v>
       </c>
       <c r="D86">
-        <v>317.4297875468667</v>
+        <v>314.1575497893612</v>
       </c>
       <c r="E86">
-        <v>228.9639999999999</v>
+        <v>237.285</v>
       </c>
       <c r="F86">
-        <v>698.9639999999999</v>
+        <v>707.285</v>
       </c>
       <c r="G86">
         <v>33.3</v>
@@ -8339,37 +8339,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M86">
-        <v>102.6079152</v>
+        <v>103.829438</v>
       </c>
       <c r="N86">
-        <v>-10.38291520000001</v>
+        <v>-11.60443800000002</v>
       </c>
       <c r="O86">
-        <v>-2.589499050880003</v>
+        <v>-2.894146837200004</v>
       </c>
       <c r="P86">
-        <v>-7.79341614912001</v>
+        <v>-8.710291162800011</v>
       </c>
       <c r="Q86">
-        <v>32.10658385087999</v>
+        <v>31.18970883719999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1729014147545164</v>
+        <v>0.1813748424048174</v>
       </c>
       <c r="T86">
-        <v>2.93536754629368</v>
+        <v>3.131058716046591</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.22416316475359</v>
+        <v>0.2215259510506067</v>
       </c>
       <c r="W86">
-        <v>0.113892847414173</v>
+        <v>0.114279990385771</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8988098025404573</v>
+        <v>0.8882355695693931</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1243442181886279</v>
+        <v>0.1253542181886279</v>
       </c>
       <c r="C87">
-        <v>-359.8274502106388</v>
+        <v>-371.3539123378284</v>
       </c>
       <c r="D87">
-        <v>314.1575497893612</v>
+        <v>310.9520876621716</v>
       </c>
       <c r="E87">
-        <v>237.285</v>
+        <v>245.606</v>
       </c>
       <c r="F87">
-        <v>707.285</v>
+        <v>715.606</v>
       </c>
       <c r="G87">
         <v>33.3</v>
@@ -8421,37 +8421,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M87">
-        <v>103.829438</v>
+        <v>105.0509608</v>
       </c>
       <c r="N87">
-        <v>-11.60443800000002</v>
+        <v>-12.82596080000002</v>
       </c>
       <c r="O87">
-        <v>-2.894146837200004</v>
+        <v>-3.198794623520005</v>
       </c>
       <c r="P87">
-        <v>-8.710291162800011</v>
+        <v>-9.627166176480014</v>
       </c>
       <c r="Q87">
-        <v>31.18970883719999</v>
+        <v>30.27283382351998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1813748424048174</v>
+        <v>0.1910587597194472</v>
       </c>
       <c r="T87">
-        <v>3.131058716046591</v>
+        <v>3.354705767192776</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2215259510506067</v>
+        <v>0.2189500678988554</v>
       </c>
       <c r="W87">
-        <v>0.114279990385771</v>
+        <v>0.114658130032448</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8882355695693931</v>
+        <v>0.8779072489930048</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1253542181886279</v>
+        <v>0.1263642181886279</v>
       </c>
       <c r="C88">
-        <v>-371.3539123378284</v>
+        <v>-382.8156221967132</v>
       </c>
       <c r="D88">
-        <v>310.9520876621716</v>
+        <v>307.8113778032869</v>
       </c>
       <c r="E88">
-        <v>245.606</v>
+        <v>253.927</v>
       </c>
       <c r="F88">
-        <v>715.606</v>
+        <v>723.927</v>
       </c>
       <c r="G88">
         <v>33.3</v>
@@ -8503,37 +8503,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M88">
-        <v>105.0509608</v>
+        <v>106.2724836</v>
       </c>
       <c r="N88">
-        <v>-12.82596080000002</v>
+        <v>-14.04748360000002</v>
       </c>
       <c r="O88">
-        <v>-3.198794623520005</v>
+        <v>-3.503442409840005</v>
       </c>
       <c r="P88">
-        <v>-9.627166176480014</v>
+        <v>-10.54404119016002</v>
       </c>
       <c r="Q88">
-        <v>30.27283382351998</v>
+        <v>29.35595880983998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1910587597194472</v>
+        <v>0.2022325104670971</v>
       </c>
       <c r="T88">
-        <v>3.354705767192776</v>
+        <v>3.612760056976837</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2189500678988554</v>
+        <v>0.2164334004517421</v>
       </c>
       <c r="W88">
-        <v>0.114658130032448</v>
+        <v>0.1150275768136843</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8779072489930048</v>
+        <v>0.867816361073545</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1263642181886279</v>
+        <v>0.1273742181886279</v>
       </c>
       <c r="C89">
-        <v>-382.8156221967132</v>
+        <v>-394.2145222204437</v>
       </c>
       <c r="D89">
-        <v>307.8113778032869</v>
+        <v>304.7334777795564</v>
       </c>
       <c r="E89">
-        <v>253.927</v>
+        <v>262.248</v>
       </c>
       <c r="F89">
-        <v>723.927</v>
+        <v>732.248</v>
       </c>
       <c r="G89">
         <v>33.3</v>
@@ -8585,37 +8585,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M89">
-        <v>106.2724836</v>
+        <v>107.4940064</v>
       </c>
       <c r="N89">
-        <v>-14.04748360000002</v>
+        <v>-15.26900640000002</v>
       </c>
       <c r="O89">
-        <v>-3.503442409840005</v>
+        <v>-3.808090196160006</v>
       </c>
       <c r="P89">
-        <v>-10.54404119016002</v>
+        <v>-11.46091620384002</v>
       </c>
       <c r="Q89">
-        <v>29.35595880983998</v>
+        <v>28.43908379615998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2022325104670971</v>
+        <v>0.2152685530060218</v>
       </c>
       <c r="T89">
-        <v>3.612760056976837</v>
+        <v>3.91382339505824</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2164334004517421</v>
+        <v>0.2139739299920632</v>
       </c>
       <c r="W89">
-        <v>0.1150275768136843</v>
+        <v>0.1153886270771651</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.867816361073545</v>
+        <v>0.857954811515891</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1273742181886279</v>
+        <v>0.1283842181886279</v>
       </c>
       <c r="C90">
-        <v>-394.2145222204437</v>
+        <v>-405.5524779194148</v>
       </c>
       <c r="D90">
-        <v>304.7334777795564</v>
+        <v>301.7165220805853</v>
       </c>
       <c r="E90">
-        <v>262.248</v>
+        <v>270.5690000000001</v>
       </c>
       <c r="F90">
-        <v>732.248</v>
+        <v>740.5690000000001</v>
       </c>
       <c r="G90">
         <v>33.3</v>
@@ -8667,37 +8667,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M90">
-        <v>107.4940064</v>
+        <v>108.7155292</v>
       </c>
       <c r="N90">
-        <v>-15.26900640000002</v>
+        <v>-16.49052920000003</v>
       </c>
       <c r="O90">
-        <v>-3.808090196160006</v>
+        <v>-4.112737982480007</v>
       </c>
       <c r="P90">
-        <v>-11.46091620384002</v>
+        <v>-12.37779121752002</v>
       </c>
       <c r="Q90">
-        <v>28.43908379615998</v>
+        <v>27.52220878247998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2152685530060218</v>
+        <v>0.2306747850974784</v>
       </c>
       <c r="T90">
-        <v>3.91382339505824</v>
+        <v>4.269625521881717</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2139739299920632</v>
+        <v>0.2115697285314782</v>
       </c>
       <c r="W90">
-        <v>0.1153886270771651</v>
+        <v>0.115741563851579</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.857954811515891</v>
+        <v>0.8483148698134653</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1283842181886279</v>
+        <v>0.1293942181886279</v>
       </c>
       <c r="C91">
-        <v>-405.5524779194148</v>
+        <v>-416.8312816517308</v>
       </c>
       <c r="D91">
-        <v>301.7165220805853</v>
+        <v>298.7587183482692</v>
       </c>
       <c r="E91">
-        <v>270.5690000000001</v>
+        <v>278.89</v>
       </c>
       <c r="F91">
-        <v>740.5690000000001</v>
+        <v>748.89</v>
       </c>
       <c r="G91">
         <v>33.3</v>
@@ -8749,37 +8749,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M91">
-        <v>108.7155292</v>
+        <v>109.937052</v>
       </c>
       <c r="N91">
-        <v>-16.49052920000003</v>
+        <v>-17.71205200000001</v>
       </c>
       <c r="O91">
-        <v>-4.112737982480007</v>
+        <v>-4.417385768800004</v>
       </c>
       <c r="P91">
-        <v>-12.37779121752002</v>
+        <v>-13.29466623120001</v>
       </c>
       <c r="Q91">
-        <v>27.52220878247998</v>
+        <v>26.60533376879999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2306747850974784</v>
+        <v>0.2491622636072262</v>
       </c>
       <c r="T91">
-        <v>4.269625521881717</v>
+        <v>4.696588074069888</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2115697285314782</v>
+        <v>0.2092189537700174</v>
       </c>
       <c r="W91">
-        <v>0.115741563851579</v>
+        <v>0.1160866575865614</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8483148698134653</v>
+        <v>0.8388891490377601</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1293942181886279</v>
+        <v>0.1304042181886279</v>
       </c>
       <c r="C92">
-        <v>-416.8312816517308</v>
+        <v>-428.0526561740501</v>
       </c>
       <c r="D92">
-        <v>298.7587183482692</v>
+        <v>295.8583438259499</v>
       </c>
       <c r="E92">
-        <v>278.89</v>
+        <v>287.211</v>
       </c>
       <c r="F92">
-        <v>748.89</v>
+        <v>757.211</v>
       </c>
       <c r="G92">
         <v>33.3</v>
@@ -8831,37 +8831,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M92">
-        <v>109.937052</v>
+        <v>111.1585748</v>
       </c>
       <c r="N92">
-        <v>-17.71205200000001</v>
+        <v>-18.93357480000002</v>
       </c>
       <c r="O92">
-        <v>-4.417385768800004</v>
+        <v>-4.722033555120005</v>
       </c>
       <c r="P92">
-        <v>-13.29466623120001</v>
+        <v>-14.21154124488001</v>
       </c>
       <c r="Q92">
-        <v>26.60533376879999</v>
+        <v>25.68845875511999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2491622636072262</v>
+        <v>0.2717580706746958</v>
       </c>
       <c r="T92">
-        <v>4.696588074069888</v>
+        <v>5.218431193410988</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2092189537700174</v>
+        <v>0.2069198443879293</v>
       </c>
       <c r="W92">
-        <v>0.1160866575865614</v>
+        <v>0.116424166843852</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8388891490377601</v>
+        <v>0.8296705869604222</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1304042181886279</v>
+        <v>0.1314142181886279</v>
       </c>
       <c r="C93">
-        <v>-428.0526561740501</v>
+        <v>-439.2182579875831</v>
       </c>
       <c r="D93">
-        <v>295.8583438259499</v>
+        <v>293.013742012417</v>
       </c>
       <c r="E93">
-        <v>287.211</v>
+        <v>295.532</v>
       </c>
       <c r="F93">
-        <v>757.211</v>
+        <v>765.532</v>
       </c>
       <c r="G93">
         <v>33.3</v>
@@ -8913,37 +8913,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M93">
-        <v>111.1585748</v>
+        <v>112.3800976</v>
       </c>
       <c r="N93">
-        <v>-18.93357480000002</v>
+        <v>-20.15509760000002</v>
       </c>
       <c r="O93">
-        <v>-4.722033555120005</v>
+        <v>-5.026681341440005</v>
       </c>
       <c r="P93">
-        <v>-14.21154124488001</v>
+        <v>-15.12841625856001</v>
       </c>
       <c r="Q93">
-        <v>25.68845875511999</v>
+        <v>24.77158374143998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2717580706746958</v>
+        <v>0.3000028295090329</v>
       </c>
       <c r="T93">
-        <v>5.218431193410988</v>
+        <v>5.870735092587363</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2069198443879293</v>
+        <v>0.2046707156445822</v>
       </c>
       <c r="W93">
-        <v>0.116424166843852</v>
+        <v>0.1167543389433753</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8296705869604222</v>
+        <v>0.8206524284065044</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1314142181886279</v>
+        <v>0.1324242181886279</v>
       </c>
       <c r="C94">
-        <v>-439.2182579875831</v>
+        <v>-450.3296804929055</v>
       </c>
       <c r="D94">
-        <v>293.013742012417</v>
+        <v>290.2233195070945</v>
       </c>
       <c r="E94">
-        <v>295.532</v>
+        <v>303.8530000000001</v>
       </c>
       <c r="F94">
-        <v>765.532</v>
+        <v>773.8530000000001</v>
       </c>
       <c r="G94">
         <v>33.3</v>
@@ -8995,37 +8995,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M94">
-        <v>112.3800976</v>
+        <v>113.6016204</v>
       </c>
       <c r="N94">
-        <v>-20.15509760000002</v>
+        <v>-21.37662040000002</v>
       </c>
       <c r="O94">
-        <v>-5.026681341440005</v>
+        <v>-5.331329127760005</v>
       </c>
       <c r="P94">
-        <v>-15.12841625856001</v>
+        <v>-16.04529127224001</v>
       </c>
       <c r="Q94">
-        <v>24.77158374143998</v>
+        <v>23.85470872775998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3000028295090329</v>
+        <v>0.3363175194388947</v>
       </c>
       <c r="T94">
-        <v>5.870735092587363</v>
+        <v>6.709411534385558</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2046707156445822</v>
+        <v>0.2024699552613071</v>
       </c>
       <c r="W94">
-        <v>0.1167543389433753</v>
+        <v>0.1170774105676401</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8206524284065044</v>
+        <v>0.8118282087462194</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1324242181886279</v>
+        <v>0.1334342181886279</v>
       </c>
       <c r="C95">
-        <v>-450.3296804929055</v>
+        <v>-461.3884569662096</v>
       </c>
       <c r="D95">
-        <v>290.2233195070945</v>
+        <v>287.4855430337905</v>
       </c>
       <c r="E95">
-        <v>303.8530000000001</v>
+        <v>312.1740000000001</v>
       </c>
       <c r="F95">
-        <v>773.8530000000001</v>
+        <v>782.1740000000001</v>
       </c>
       <c r="G95">
         <v>33.3</v>
@@ -9077,37 +9077,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M95">
-        <v>113.6016204</v>
+        <v>114.8231432</v>
       </c>
       <c r="N95">
-        <v>-21.37662040000002</v>
+        <v>-22.59814320000002</v>
       </c>
       <c r="O95">
-        <v>-5.331329127760005</v>
+        <v>-5.635976914080006</v>
       </c>
       <c r="P95">
-        <v>-16.04529127224001</v>
+        <v>-16.96216628592002</v>
       </c>
       <c r="Q95">
-        <v>23.85470872775998</v>
+        <v>22.93783371407998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3363175194388947</v>
+        <v>0.3847371060120439</v>
       </c>
       <c r="T95">
-        <v>6.709411534385558</v>
+        <v>7.827646790116486</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2024699552613071</v>
+        <v>0.2003160195670379</v>
       </c>
       <c r="W95">
-        <v>0.1170774105676401</v>
+        <v>0.1173936083275588</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8118282087462194</v>
+        <v>0.8031917384404086</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1334342181886279</v>
+        <v>0.1870128828251968</v>
       </c>
       <c r="C96">
-        <v>-461.3884569662096</v>
+        <v>-565.591846110263</v>
       </c>
       <c r="D96">
-        <v>287.4855430337905</v>
+        <v>191.6031538897371</v>
       </c>
       <c r="E96">
-        <v>312.1740000000001</v>
+        <v>320.4950000000001</v>
       </c>
       <c r="F96">
-        <v>782.1740000000001</v>
+        <v>790.4950000000001</v>
       </c>
       <c r="G96">
         <v>33.3</v>
@@ -9159,45 +9159,45 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M96">
-        <v>114.8231432</v>
+        <v>158.731396</v>
       </c>
       <c r="N96">
-        <v>-22.59814320000002</v>
+        <v>-66.50639600000002</v>
       </c>
       <c r="O96">
-        <v>-5.635976914080006</v>
+        <v>-16.58669516240001</v>
       </c>
       <c r="P96">
-        <v>-16.96216628592002</v>
+        <v>-49.91970083760002</v>
       </c>
       <c r="Q96">
-        <v>22.93783371407998</v>
+        <v>-10.01970083760002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3847371060120439</v>
+        <v>0.4778978199458314</v>
       </c>
       <c r="T96">
-        <v>7.827646790116486</v>
+        <v>9.97916443292913</v>
       </c>
       <c r="U96">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.2003160195670379</v>
+        <v>0.1449046349973511</v>
       </c>
       <c r="W96">
-        <v>0.1173936083275588</v>
+        <v>0.1717031492925319</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.8031917384404086</v>
+        <v>0.5810129711200926</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1870128828251968</v>
+        <v>0.1885628828251969</v>
       </c>
       <c r="C97">
-        <v>-565.591846110263</v>
+        <v>-575.7438744739861</v>
       </c>
       <c r="D97">
-        <v>191.6031538897371</v>
+        <v>189.7721255260139</v>
       </c>
       <c r="E97">
-        <v>320.4950000000001</v>
+        <v>328.816</v>
       </c>
       <c r="F97">
-        <v>790.4950000000001</v>
+        <v>798.816</v>
       </c>
       <c r="G97">
         <v>33.3</v>
@@ -9241,37 +9241,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M97">
-        <v>158.731396</v>
+        <v>160.4022528</v>
       </c>
       <c r="N97">
-        <v>-66.50639600000002</v>
+        <v>-68.17725280000002</v>
       </c>
       <c r="O97">
-        <v>-16.58669516240001</v>
+        <v>-17.00340684832</v>
       </c>
       <c r="P97">
-        <v>-49.91970083760002</v>
+        <v>-51.17384595168001</v>
       </c>
       <c r="Q97">
-        <v>-10.01970083760002</v>
+        <v>-11.27384595168002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4778978199458314</v>
+        <v>0.5859222749322894</v>
       </c>
       <c r="T97">
-        <v>9.97916443292913</v>
+        <v>12.47395554116142</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1449046349973511</v>
+        <v>0.1433952117161287</v>
       </c>
       <c r="W97">
-        <v>0.1717031492925319</v>
+        <v>0.1720062414874014</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5810129711200926</v>
+        <v>0.5749607526709251</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1885628828251968</v>
+        <v>0.1901128828251968</v>
       </c>
       <c r="C98">
-        <v>-575.7438744739861</v>
+        <v>-585.8612381798943</v>
       </c>
       <c r="D98">
-        <v>189.7721255260139</v>
+        <v>187.9757618201057</v>
       </c>
       <c r="E98">
-        <v>328.816</v>
+        <v>337.1369999999999</v>
       </c>
       <c r="F98">
-        <v>798.816</v>
+        <v>807.1369999999999</v>
       </c>
       <c r="G98">
         <v>33.3</v>
@@ -9323,37 +9323,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M98">
-        <v>160.4022528</v>
+        <v>162.0731096</v>
       </c>
       <c r="N98">
-        <v>-68.17725280000002</v>
+        <v>-69.84810959999999</v>
       </c>
       <c r="O98">
-        <v>-17.00340684832</v>
+        <v>-17.42011853424</v>
       </c>
       <c r="P98">
-        <v>-51.17384595168001</v>
+        <v>-52.42799106575999</v>
       </c>
       <c r="Q98">
-        <v>-11.27384595168002</v>
+        <v>-12.52799106575999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.585922274932288</v>
+        <v>0.7659630332430507</v>
       </c>
       <c r="T98">
-        <v>12.47395554116138</v>
+        <v>16.63194072154851</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1433952117161287</v>
+        <v>0.141916910564416</v>
       </c>
       <c r="W98">
-        <v>0.1720062414874014</v>
+        <v>0.1723030843586653</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5749607526709251</v>
+        <v>0.5690333222310187</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1901128828251968</v>
+        <v>0.1916628828251969</v>
       </c>
       <c r="C99">
-        <v>-585.8612381798943</v>
+        <v>-595.9449123935814</v>
       </c>
       <c r="D99">
-        <v>187.9757618201057</v>
+        <v>186.2130876064186</v>
       </c>
       <c r="E99">
-        <v>337.1369999999999</v>
+        <v>345.458</v>
       </c>
       <c r="F99">
-        <v>807.1369999999999</v>
+        <v>815.458</v>
       </c>
       <c r="G99">
         <v>33.3</v>
@@ -9405,37 +9405,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M99">
-        <v>162.0731096</v>
+        <v>163.7439664</v>
       </c>
       <c r="N99">
-        <v>-69.84810959999999</v>
+        <v>-71.51896640000001</v>
       </c>
       <c r="O99">
-        <v>-17.42011853424</v>
+        <v>-17.83683022016</v>
       </c>
       <c r="P99">
-        <v>-52.42799106575999</v>
+        <v>-53.68213617984001</v>
       </c>
       <c r="Q99">
-        <v>-12.52799106575999</v>
+        <v>-13.78213617984001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7659630332430507</v>
+        <v>1.126044549864576</v>
       </c>
       <c r="T99">
-        <v>16.63194072154851</v>
+        <v>24.94791108232277</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.141916910564416</v>
+        <v>0.1404687788239628</v>
       </c>
       <c r="W99">
-        <v>0.1723030843586653</v>
+        <v>0.1725938692121483</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5690333222310187</v>
+        <v>0.5632268597592736</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1916628828251969</v>
+        <v>0.1932128828251968</v>
       </c>
       <c r="C100">
-        <v>-595.9449123935814</v>
+        <v>-605.9958360434023</v>
       </c>
       <c r="D100">
-        <v>186.2130876064186</v>
+        <v>184.4831639565977</v>
       </c>
       <c r="E100">
-        <v>345.458</v>
+        <v>353.779</v>
       </c>
       <c r="F100">
-        <v>815.458</v>
+        <v>823.779</v>
       </c>
       <c r="G100">
         <v>33.3</v>
@@ -9487,37 +9487,37 @@
         <v>92.22499999999999</v>
       </c>
       <c r="M100">
-        <v>163.7439664</v>
+        <v>165.4148232</v>
       </c>
       <c r="N100">
-        <v>-71.51896640000001</v>
+        <v>-73.18982320000001</v>
       </c>
       <c r="O100">
-        <v>-17.83683022016</v>
+        <v>-18.25354190608</v>
       </c>
       <c r="P100">
-        <v>-53.68213617984001</v>
+        <v>-54.93628129392</v>
       </c>
       <c r="Q100">
-        <v>-13.78213617984001</v>
+        <v>-15.03628129392001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.126044549864576</v>
+        <v>2.206289099729152</v>
       </c>
       <c r="T100">
-        <v>24.94791108232277</v>
+        <v>49.89582216464554</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1404687788239628</v>
+        <v>0.1390499022701854</v>
       </c>
       <c r="W100">
-        <v>0.1725938692121483</v>
+        <v>0.1728787796241468</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5632268597592736</v>
+        <v>0.5575376995596849</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1932128828251968</v>
-      </c>
-      <c r="C101">
-        <v>-605.9958360434023</v>
-      </c>
-      <c r="D101">
-        <v>184.4831639565977</v>
-      </c>
-      <c r="E101">
-        <v>353.779</v>
-      </c>
-      <c r="F101">
-        <v>823.779</v>
-      </c>
-      <c r="G101">
-        <v>33.3</v>
-      </c>
-      <c r="H101">
-        <v>362.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>132.125</v>
-      </c>
-      <c r="K101">
-        <v>39.9</v>
-      </c>
-      <c r="L101">
-        <v>92.22499999999999</v>
-      </c>
-      <c r="M101">
-        <v>165.4148232</v>
-      </c>
-      <c r="N101">
-        <v>-73.18982320000001</v>
-      </c>
-      <c r="O101">
-        <v>-18.25354190608</v>
-      </c>
-      <c r="P101">
-        <v>-54.93628129392</v>
-      </c>
-      <c r="Q101">
-        <v>-15.03628129392001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.206289099729152</v>
-      </c>
-      <c r="T101">
-        <v>49.89582216464554</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1390499022701854</v>
-      </c>
-      <c r="W101">
-        <v>0.1728787796241468</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5575376995596849</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
